--- a/Зачетная работа за 4 семестр/Орг.структура.xlsx
+++ b/Зачетная работа за 4 семестр/Орг.структура.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Типа рабочий стол\Колледжные дела\BD\Зачетная работа за 4 семестр\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D41EC23-0D50-4F94-9CD7-38A246919B46}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14745" windowHeight="9285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="TDSheet" sheetId="1" r:id="rId4"/>
+    <sheet name="TDSheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="nMhsS1P6EpcUcU6FKOXqQxU3+idsa6iNDH4ih6mhp30="/>
@@ -1384,47 +1393,59 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1438,21 +1459,36 @@
         <bgColor rgb="FFF8F2D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFCCC085"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FFCCC085"/>
       </top>
       <bottom style="thin">
         <color rgb="FFCCC085"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FFCCC085"/>
       </right>
@@ -1462,6 +1498,7 @@
       <bottom style="thin">
         <color rgb="FFCCC085"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1473,6 +1510,8 @@
       <top style="thin">
         <color rgb="FFCCC085"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1481,6 +1520,9 @@
       <right style="thin">
         <color rgb="FFCCC085"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1495,6 +1537,7 @@
       <bottom style="thin">
         <color rgb="FFCCC085"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1503,91 +1546,102 @@
       <right style="thin">
         <color rgb="FFCCC085"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FFCCC085"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="3" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{6CCE7DFD-306B-4EE3-BEC3-19639D3371CF}"/>
+    <cellStyle name="Обычный 2 2" xfId="2" xr:uid="{CE849933-A9E1-43CD-B87F-E5A5E578981F}"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1777,38 +1831,41 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="16.83" defaultRowHeight="15.0" outlineLevelRow="4"/>
+  <dimension ref="A1:Y1008"/>
+  <sheetFormatPr defaultColWidth="16.83203125" defaultRowHeight="15" customHeight="1" outlineLevelRow="4" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="68.17"/>
-    <col customWidth="1" min="2" max="2" width="34.0"/>
-    <col customWidth="1" min="3" max="3" width="12.17"/>
-    <col customWidth="1" min="4" max="4" width="19.0"/>
-    <col customWidth="1" min="5" max="5" width="12.0"/>
-    <col customWidth="1" min="6" max="6" width="22.0"/>
-    <col customWidth="1" min="7" max="25" width="10.5"/>
+    <col min="1" max="1" width="68.1640625" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="25" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="6.75" customHeight="1">
+      <c r="B2" s="18"/>
+    </row>
+    <row r="3" spans="1:25" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1835,6472 +1892,6521 @@
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
     </row>
-    <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+    </row>
+    <row r="6" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" ht="10.5" customHeight="1">
-      <c r="A7" s="11" t="s">
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+    </row>
+    <row r="7" spans="1:25" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="12"/>
-    </row>
-    <row r="8" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A8" s="13" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:25" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="14"/>
-    </row>
-    <row r="9" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A9" s="13" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:25" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="14"/>
-      <c r="E9" s="15"/>
-    </row>
-    <row r="10" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A10" s="16" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="5"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:25" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="17">
-        <v>26048.0</v>
-      </c>
-      <c r="D10" s="18" t="s">
+      <c r="C10" s="8">
+        <v>26048</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:25" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="17">
-        <v>32679.0</v>
-      </c>
-      <c r="D11" s="18" t="s">
+      <c r="C11" s="8">
+        <v>32679</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:25" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="20"/>
-    </row>
-    <row r="13" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A13" s="16" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="13" spans="1:25" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="17">
-        <v>28959.0</v>
-      </c>
-      <c r="D13" s="18" t="s">
+      <c r="C13" s="8">
+        <v>28959</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="19">
-        <v>482.0</v>
-      </c>
-      <c r="F13" s="20" t="s">
+      <c r="E13" s="10">
+        <v>482</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A14" s="16" t="s">
+    <row r="14" spans="1:25" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="17">
-        <v>24610.0</v>
-      </c>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="8">
+        <v>24610</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="19">
-        <v>482.0</v>
-      </c>
-      <c r="F14" s="20" t="s">
+      <c r="E14" s="10">
+        <v>482</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A15" s="16" t="s">
+    <row r="15" spans="1:25" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="17">
-        <v>26166.0</v>
-      </c>
-      <c r="D15" s="18" t="s">
+      <c r="C15" s="8">
+        <v>26166</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="19">
-        <v>482.0</v>
-      </c>
-      <c r="F15" s="20" t="s">
+      <c r="E15" s="10">
+        <v>482</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:25" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="20"/>
-    </row>
-    <row r="17" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A17" s="16" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="17">
-        <v>25218.0</v>
-      </c>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="8">
+        <v>25218</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F17" s="20" t="s">
+      <c r="E17" s="10">
+        <v>479</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A18" s="16" t="s">
+    <row r="18" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="17">
-        <v>23740.0</v>
-      </c>
-      <c r="D18" s="18" t="s">
+      <c r="C18" s="8">
+        <v>23740</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F18" s="20" t="s">
+      <c r="E18" s="10">
+        <v>479</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="19" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A19" s="16" t="s">
+    <row r="19" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="17">
-        <v>30825.0</v>
-      </c>
-      <c r="D19" s="18" t="s">
+      <c r="C19" s="8">
+        <v>30825</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F19" s="20" t="s">
+      <c r="E19" s="10">
+        <v>479</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A20" s="16" t="s">
+    <row r="20" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="17">
-        <v>28474.0</v>
-      </c>
-      <c r="D20" s="18" t="s">
+      <c r="C20" s="8">
+        <v>28474</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F20" s="20" t="s">
+      <c r="E20" s="10">
+        <v>479</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A21" s="16" t="s">
+    <row r="21" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="17">
-        <v>35198.0</v>
-      </c>
-      <c r="D21" s="18" t="s">
+      <c r="C21" s="8">
+        <v>35198</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F21" s="20" t="s">
+      <c r="E21" s="10">
+        <v>479</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A22" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A23" s="16" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="17">
-        <v>32930.0</v>
-      </c>
-      <c r="D23" s="18" t="s">
+      <c r="C23" s="8">
+        <v>32930</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="19">
-        <v>482.0</v>
-      </c>
-      <c r="F23" s="20" t="s">
+      <c r="E23" s="10">
+        <v>482</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A24" s="16" t="s">
+    <row r="24" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="17">
-        <v>27698.0</v>
-      </c>
-      <c r="D24" s="18" t="s">
+      <c r="C24" s="8">
+        <v>27698</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E24" s="19">
-        <v>482.0</v>
-      </c>
-      <c r="F24" s="20" t="s">
+      <c r="E24" s="10">
+        <v>482</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A25" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="20"/>
-    </row>
-    <row r="26" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A26" s="16" t="s">
+      <c r="B25" s="15"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="17">
-        <v>36379.0</v>
-      </c>
-      <c r="D26" s="18" t="s">
+      <c r="C26" s="8">
+        <v>36379</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="19">
-        <v>483.0</v>
-      </c>
-      <c r="F26" s="20" t="s">
+      <c r="E26" s="10">
+        <v>483</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="27" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A27" s="16" t="s">
+    <row r="27" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="17">
-        <v>23402.0</v>
-      </c>
-      <c r="D27" s="18" t="s">
+      <c r="C27" s="8">
+        <v>23402</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="19">
-        <v>483.0</v>
-      </c>
-      <c r="F27" s="20" t="s">
+      <c r="E27" s="10">
+        <v>483</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A28" s="13" t="s">
+    <row r="28" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A28" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A29" s="13" t="s">
+      <c r="B28" s="15"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A29" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" s="20"/>
-    </row>
-    <row r="30" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A30" s="16" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="17">
-        <v>35345.0</v>
-      </c>
-      <c r="D30" s="18" t="s">
+      <c r="C30" s="8">
+        <v>35345</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="19">
-        <v>483.0</v>
-      </c>
-      <c r="F30" s="20" t="s">
+      <c r="E30" s="10">
+        <v>483</v>
+      </c>
+      <c r="F30" s="11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="31" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="17">
-        <v>26055.0</v>
-      </c>
-      <c r="D31" s="18" t="s">
+      <c r="C31" s="8">
+        <v>26055</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="19">
-        <v>483.0</v>
-      </c>
-      <c r="F31" s="20" t="s">
+      <c r="E31" s="10">
+        <v>483</v>
+      </c>
+      <c r="F31" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="32" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A32" s="13" t="s">
+    <row r="32" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A32" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="20"/>
-    </row>
-    <row r="33" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A33" s="16" t="s">
+      <c r="B32" s="15"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="11"/>
+    </row>
+    <row r="33" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="17">
-        <v>30970.0</v>
-      </c>
-      <c r="D33" s="18" t="s">
+      <c r="C33" s="8">
+        <v>30970</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E33" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F33" s="20" t="s">
+      <c r="E33" s="10">
+        <v>525</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A34" s="16" t="s">
+    <row r="34" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="17">
-        <v>24955.0</v>
-      </c>
-      <c r="D34" s="18" t="s">
+      <c r="C34" s="8">
+        <v>24955</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F34" s="20" t="s">
+      <c r="E34" s="10">
+        <v>525</v>
+      </c>
+      <c r="F34" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="35" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A35" s="16" t="s">
+    <row r="35" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="17">
-        <v>22093.0</v>
-      </c>
-      <c r="D35" s="18" t="s">
+      <c r="C35" s="8">
+        <v>22093</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F35" s="20" t="s">
+      <c r="E35" s="10">
+        <v>525</v>
+      </c>
+      <c r="F35" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="36" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A36" s="16" t="s">
+    <row r="36" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="17">
-        <v>29228.0</v>
-      </c>
-      <c r="D36" s="18" t="s">
+      <c r="C36" s="8">
+        <v>29228</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F36" s="20" t="s">
+      <c r="E36" s="10">
+        <v>525</v>
+      </c>
+      <c r="F36" s="11" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="37" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A37" s="16" t="s">
+    <row r="37" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="17">
-        <v>32316.0</v>
-      </c>
-      <c r="D37" s="18" t="s">
+      <c r="C37" s="8">
+        <v>32316</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E37" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F37" s="20" t="s">
+      <c r="E37" s="10">
+        <v>525</v>
+      </c>
+      <c r="F37" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="38" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A38" s="16" t="s">
+    <row r="38" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A38" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="17">
-        <v>36063.0</v>
-      </c>
-      <c r="D38" s="18" t="s">
+      <c r="C38" s="8">
+        <v>36063</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E38" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F38" s="20" t="s">
+      <c r="E38" s="10">
+        <v>525</v>
+      </c>
+      <c r="F38" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="39" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A39" s="16" t="s">
+    <row r="39" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A39" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="17">
-        <v>24220.0</v>
-      </c>
-      <c r="D39" s="18" t="s">
+      <c r="C39" s="8">
+        <v>24220</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E39" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F39" s="20" t="s">
+      <c r="E39" s="10">
+        <v>525</v>
+      </c>
+      <c r="F39" s="11" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="40" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A40" s="16" t="s">
+    <row r="40" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A40" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="17">
-        <v>37040.0</v>
-      </c>
-      <c r="D40" s="18" t="s">
+      <c r="C40" s="8">
+        <v>37040</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E40" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F40" s="20" t="s">
+      <c r="E40" s="10">
+        <v>525</v>
+      </c>
+      <c r="F40" s="11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="41" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A41" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="17">
-        <v>35450.0</v>
-      </c>
-      <c r="D41" s="18" t="s">
+      <c r="C41" s="8">
+        <v>35450</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E41" s="19">
-        <v>525.0</v>
-      </c>
-      <c r="F41" s="20" t="s">
+      <c r="E41" s="10">
+        <v>525</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="42" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A42" s="13" t="s">
+    <row r="42" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A42" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F42" s="20"/>
-    </row>
-    <row r="43" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A43" s="16" t="s">
+      <c r="B42" s="15"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A43" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="17">
-        <v>30431.0</v>
-      </c>
-      <c r="D43" s="18" t="s">
+      <c r="C43" s="8">
+        <v>30431</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E43" s="19">
-        <v>489.0</v>
-      </c>
-      <c r="F43" s="20" t="s">
+      <c r="E43" s="10">
+        <v>489</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="44" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A44" s="16" t="s">
+    <row r="44" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A44" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C44" s="17">
-        <v>24568.0</v>
-      </c>
-      <c r="D44" s="18" t="s">
+      <c r="C44" s="8">
+        <v>24568</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E44" s="19">
-        <v>489.0</v>
-      </c>
-      <c r="F44" s="20" t="s">
+      <c r="E44" s="10">
+        <v>489</v>
+      </c>
+      <c r="F44" s="11" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="45" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A45" s="13" t="s">
+    <row r="45" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A45" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F45" s="20"/>
-    </row>
-    <row r="46" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A46" s="16" t="s">
+      <c r="B45" s="15"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A46" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C46" s="17">
-        <v>37475.0</v>
-      </c>
-      <c r="D46" s="18" t="s">
+      <c r="C46" s="8">
+        <v>37475</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E46" s="19">
-        <v>527.0</v>
-      </c>
-      <c r="F46" s="20" t="s">
+      <c r="E46" s="10">
+        <v>527</v>
+      </c>
+      <c r="F46" s="11" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="47" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A47" s="16" t="s">
+    <row r="47" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A47" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="17">
-        <v>36710.0</v>
-      </c>
-      <c r="D47" s="18" t="s">
+      <c r="C47" s="8">
+        <v>36710</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E47" s="19">
-        <v>527.0</v>
-      </c>
-      <c r="F47" s="20" t="s">
+      <c r="E47" s="10">
+        <v>527</v>
+      </c>
+      <c r="F47" s="11" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="48" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A48" s="16" t="s">
+    <row r="48" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A48" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C48" s="17">
-        <v>24936.0</v>
-      </c>
-      <c r="D48" s="18" t="s">
+      <c r="C48" s="8">
+        <v>24936</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E48" s="19">
-        <v>527.0</v>
-      </c>
-      <c r="F48" s="20" t="s">
+      <c r="E48" s="10">
+        <v>527</v>
+      </c>
+      <c r="F48" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="49" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A49" s="16" t="s">
+    <row r="49" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A49" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C49" s="21">
-        <v>33026.0</v>
-      </c>
-      <c r="D49" s="18" t="s">
+      <c r="C49" s="12">
+        <v>33026</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E49" s="19">
-        <v>527.0</v>
-      </c>
-      <c r="F49" s="20" t="s">
+      <c r="E49" s="10">
+        <v>527</v>
+      </c>
+      <c r="F49" s="11" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="50" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A50" s="16" t="s">
+    <row r="50" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A50" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C50" s="17">
-        <v>24957.0</v>
-      </c>
-      <c r="D50" s="18" t="s">
+      <c r="C50" s="8">
+        <v>24957</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E50" s="19">
-        <v>527.0</v>
-      </c>
-      <c r="F50" s="20" t="s">
+      <c r="E50" s="10">
+        <v>527</v>
+      </c>
+      <c r="F50" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="51" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A51" s="16" t="s">
+    <row r="51" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A51" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C51" s="17">
-        <v>27340.0</v>
-      </c>
-      <c r="D51" s="18" t="s">
+      <c r="C51" s="8">
+        <v>27340</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E51" s="19">
-        <v>527.0</v>
-      </c>
-      <c r="F51" s="20" t="s">
+      <c r="E51" s="10">
+        <v>527</v>
+      </c>
+      <c r="F51" s="11" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="52" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A52" s="16" t="s">
+    <row r="52" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A52" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C52" s="17">
-        <v>37087.0</v>
-      </c>
-      <c r="D52" s="18" t="s">
+      <c r="C52" s="8">
+        <v>37087</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E52" s="19">
-        <v>527.0</v>
-      </c>
-      <c r="F52" s="20" t="s">
+      <c r="E52" s="10">
+        <v>527</v>
+      </c>
+      <c r="F52" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="53" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A53" s="13" t="s">
+    <row r="53" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F53" s="20"/>
-    </row>
-    <row r="54" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A54" s="13" t="s">
+      <c r="B53" s="25"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="11"/>
+    </row>
+    <row r="54" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A54" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F54" s="20"/>
-    </row>
-    <row r="55" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A55" s="16" t="s">
+      <c r="B54" s="15"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F54" s="11"/>
+    </row>
+    <row r="55" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A55" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C55" s="17">
-        <v>37612.0</v>
-      </c>
-      <c r="D55" s="18" t="s">
+      <c r="C55" s="8">
+        <v>37612</v>
+      </c>
+      <c r="D55" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="E55" s="19">
-        <v>477.0</v>
-      </c>
-      <c r="F55" s="20" t="s">
+      <c r="E55" s="10">
+        <v>477</v>
+      </c>
+      <c r="F55" s="11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="56" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A56" s="16" t="s">
+    <row r="56" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A56" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C56" s="17">
-        <v>32651.0</v>
-      </c>
-      <c r="D56" s="18" t="s">
+      <c r="C56" s="8">
+        <v>32651</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E56" s="19">
-        <v>477.0</v>
-      </c>
-      <c r="F56" s="20" t="s">
+      <c r="E56" s="10">
+        <v>477</v>
+      </c>
+      <c r="F56" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="57" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A57" s="13" t="s">
+    <row r="57" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A57" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F57" s="20"/>
-    </row>
-    <row r="58" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A58" s="16" t="s">
+      <c r="B57" s="15"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" s="11"/>
+    </row>
+    <row r="58" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A58" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C58" s="17">
-        <v>25533.0</v>
-      </c>
-      <c r="D58" s="18" t="s">
+      <c r="C58" s="8">
+        <v>25533</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E58" s="19">
-        <v>404.0</v>
-      </c>
-      <c r="F58" s="20" t="s">
+      <c r="E58" s="10">
+        <v>404</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="59" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A59" s="16" t="s">
+    <row r="59" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A59" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C59" s="17">
-        <v>33211.0</v>
-      </c>
-      <c r="D59" s="18" t="s">
+      <c r="C59" s="8">
+        <v>33211</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="E59" s="19">
-        <v>404.0</v>
-      </c>
-      <c r="F59" s="20" t="s">
+      <c r="E59" s="10">
+        <v>404</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="60" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A60" s="16" t="s">
+    <row r="60" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A60" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C60" s="17">
-        <v>25744.0</v>
-      </c>
-      <c r="D60" s="18" t="s">
+      <c r="C60" s="8">
+        <v>25744</v>
+      </c>
+      <c r="D60" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E60" s="19">
-        <v>404.0</v>
-      </c>
-      <c r="F60" s="20" t="s">
+      <c r="E60" s="10">
+        <v>404</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="61" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A61" s="16" t="s">
+    <row r="61" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A61" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C61" s="17">
-        <v>30157.0</v>
-      </c>
-      <c r="D61" s="18" t="s">
+      <c r="C61" s="8">
+        <v>30157</v>
+      </c>
+      <c r="D61" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E61" s="19">
-        <v>404.0</v>
-      </c>
-      <c r="F61" s="20" t="s">
+      <c r="E61" s="10">
+        <v>404</v>
+      </c>
+      <c r="F61" s="11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="62" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A62" s="13" t="s">
+    <row r="62" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A62" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E62" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F62" s="20"/>
-    </row>
-    <row r="63" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A63" s="16" t="s">
+      <c r="B62" s="15"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" s="11"/>
+    </row>
+    <row r="63" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A63" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C63" s="17">
-        <v>33948.0</v>
-      </c>
-      <c r="D63" s="18" t="s">
+      <c r="C63" s="8">
+        <v>33948</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="19">
-        <v>415.0</v>
-      </c>
-      <c r="F63" s="20" t="s">
+      <c r="E63" s="10">
+        <v>415</v>
+      </c>
+      <c r="F63" s="11" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="64" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A64" s="16" t="s">
+    <row r="64" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A64" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C64" s="17">
-        <v>30985.0</v>
-      </c>
-      <c r="D64" s="18" t="s">
+      <c r="C64" s="8">
+        <v>30985</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E64" s="19">
-        <v>415.0</v>
-      </c>
-      <c r="F64" s="20" t="s">
+      <c r="E64" s="10">
+        <v>415</v>
+      </c>
+      <c r="F64" s="11" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="65" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A65" s="16" t="s">
+    <row r="65" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A65" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C65" s="17">
-        <v>28939.0</v>
-      </c>
-      <c r="D65" s="18" t="s">
+      <c r="C65" s="8">
+        <v>28939</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E65" s="19">
-        <v>415.0</v>
-      </c>
-      <c r="F65" s="20" t="s">
+      <c r="E65" s="10">
+        <v>415</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="66" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A66" s="16" t="s">
+    <row r="66" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A66" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C66" s="21">
-        <v>37040.0</v>
-      </c>
-      <c r="D66" s="18" t="s">
+      <c r="C66" s="12">
+        <v>37040</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E66" s="19">
-        <v>415.0</v>
-      </c>
-      <c r="F66" s="20" t="s">
+      <c r="E66" s="10">
+        <v>415</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="67" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A67" s="13" t="s">
+    <row r="67" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A67" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F67" s="20"/>
-    </row>
-    <row r="68" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A68" s="16" t="s">
+      <c r="B67" s="15"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67" s="11"/>
+    </row>
+    <row r="68" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A68" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C68" s="17">
-        <v>34829.0</v>
-      </c>
-      <c r="D68" s="18" t="s">
+      <c r="C68" s="8">
+        <v>34829</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="E68" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F68" s="20" t="s">
+      <c r="E68" s="10">
+        <v>479</v>
+      </c>
+      <c r="F68" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="69" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A69" s="16" t="s">
+    <row r="69" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A69" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C69" s="17">
-        <v>32534.0</v>
-      </c>
-      <c r="D69" s="18" t="s">
+      <c r="C69" s="8">
+        <v>32534</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="E69" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F69" s="20" t="s">
+      <c r="E69" s="10">
+        <v>479</v>
+      </c>
+      <c r="F69" s="11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="70" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A70" s="16" t="s">
+    <row r="70" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A70" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="C70" s="17">
-        <v>31087.0</v>
-      </c>
-      <c r="D70" s="18" t="s">
+      <c r="C70" s="8">
+        <v>31087</v>
+      </c>
+      <c r="D70" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F70" s="20" t="s">
+      <c r="E70" s="10">
+        <v>479</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="71" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A71" s="16" t="s">
+    <row r="71" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A71" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C71" s="17">
-        <v>22481.0</v>
-      </c>
-      <c r="D71" s="18" t="s">
+      <c r="C71" s="8">
+        <v>22481</v>
+      </c>
+      <c r="D71" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E71" s="19">
-        <v>479.0</v>
-      </c>
-      <c r="F71" s="20" t="s">
+      <c r="E71" s="10">
+        <v>479</v>
+      </c>
+      <c r="F71" s="11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="72" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A72" s="13" t="s">
+    <row r="72" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F72" s="20"/>
-    </row>
-    <row r="73" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A73" s="16" t="s">
+      <c r="B72" s="25"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72" s="11"/>
+    </row>
+    <row r="73" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A73" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C73" s="17">
-        <v>36231.0</v>
-      </c>
-      <c r="D73" s="18" t="s">
+      <c r="C73" s="8">
+        <v>36231</v>
+      </c>
+      <c r="D73" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="E73" s="19" t="s">
+      <c r="E73" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F73" s="20" t="s">
+      <c r="F73" s="11" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="74" ht="21.75" customHeight="1" outlineLevel="2">
-      <c r="A74" s="16" t="s">
+    <row r="74" spans="1:6" ht="21.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A74" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B74" s="16" t="s">
+      <c r="B74" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C74" s="17">
-        <v>36988.0</v>
-      </c>
-      <c r="D74" s="18" t="s">
+      <c r="C74" s="8">
+        <v>36988</v>
+      </c>
+      <c r="D74" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E74" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F74" s="20" t="s">
+      <c r="F74" s="11" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="75" ht="21.75" customHeight="1" outlineLevel="2">
-      <c r="A75" s="16" t="s">
+    <row r="75" spans="1:6" ht="21.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A75" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="B75" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C75" s="17">
-        <v>33664.0</v>
-      </c>
-      <c r="D75" s="18" t="s">
+      <c r="C75" s="8">
+        <v>33664</v>
+      </c>
+      <c r="D75" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="E75" s="19" t="s">
+      <c r="E75" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F75" s="20" t="s">
+      <c r="F75" s="11" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="76" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A76" s="16" t="s">
+    <row r="76" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A76" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="C76" s="17">
-        <v>25011.0</v>
-      </c>
-      <c r="D76" s="18" t="s">
+      <c r="C76" s="8">
+        <v>25011</v>
+      </c>
+      <c r="D76" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="E76" s="19" t="s">
+      <c r="E76" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F76" s="20" t="s">
+      <c r="F76" s="11" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="77" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A77" s="16" t="s">
+    <row r="77" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A77" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C77" s="17">
-        <v>27891.0</v>
-      </c>
-      <c r="D77" s="18" t="s">
+      <c r="C77" s="8">
+        <v>27891</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="E77" s="19" t="s">
+      <c r="E77" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F77" s="20" t="s">
+      <c r="F77" s="11" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="78" ht="21.75" customHeight="1" outlineLevel="2">
-      <c r="A78" s="16" t="s">
+    <row r="78" spans="1:6" ht="11.25" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A78" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="C78" s="17">
-        <v>32415.0</v>
-      </c>
-      <c r="D78" s="18" t="s">
+      <c r="C78" s="8">
+        <v>32415</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E78" s="19" t="s">
+      <c r="E78" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F78" s="20" t="s">
+      <c r="F78" s="11" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="79" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A79" s="16" t="s">
+    <row r="79" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A79" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="C79" s="17">
-        <v>27351.0</v>
-      </c>
-      <c r="D79" s="18" t="s">
+      <c r="C79" s="8">
+        <v>27351</v>
+      </c>
+      <c r="D79" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E79" s="19" t="s">
+      <c r="E79" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F79" s="20" t="s">
+      <c r="F79" s="11" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="80" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A80" s="16" t="s">
+    <row r="80" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A80" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="C80" s="17">
-        <v>31180.0</v>
-      </c>
-      <c r="D80" s="18" t="s">
+      <c r="C80" s="8">
+        <v>31180</v>
+      </c>
+      <c r="D80" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E80" s="19" t="s">
+      <c r="E80" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F80" s="20" t="s">
+      <c r="F80" s="11" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="81" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A81" s="16" t="s">
+    <row r="81" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A81" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B81" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="C81" s="17">
-        <v>28357.0</v>
-      </c>
-      <c r="D81" s="18" t="s">
+      <c r="C81" s="8">
+        <v>28357</v>
+      </c>
+      <c r="D81" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E81" s="19" t="s">
+      <c r="E81" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F81" s="20" t="s">
+      <c r="F81" s="11" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="82" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A82" s="16" t="s">
+    <row r="82" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A82" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C82" s="17">
-        <v>28587.0</v>
-      </c>
-      <c r="D82" s="18" t="s">
+      <c r="C82" s="8">
+        <v>28587</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="E82" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F82" s="20" t="s">
+      <c r="F82" s="11" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="83" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A83" s="16" t="s">
+    <row r="83" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A83" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B83" s="16" t="s">
+      <c r="B83" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="C83" s="17">
-        <v>22385.0</v>
-      </c>
-      <c r="D83" s="18" t="s">
+      <c r="C83" s="8">
+        <v>22385</v>
+      </c>
+      <c r="D83" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="E83" s="19" t="s">
+      <c r="E83" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F83" s="20" t="s">
+      <c r="F83" s="11" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="84" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A84" s="13" t="s">
+    <row r="84" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F84" s="20"/>
-    </row>
-    <row r="85" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A85" s="13" t="s">
+      <c r="B84" s="25"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84" s="11"/>
+    </row>
+    <row r="85" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A85" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F85" s="20"/>
-    </row>
-    <row r="86" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A86" s="16" t="s">
+      <c r="B85" s="15"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85" s="11"/>
+    </row>
+    <row r="86" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A86" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B86" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="C86" s="17">
-        <v>24524.0</v>
-      </c>
-      <c r="D86" s="18" t="s">
+      <c r="C86" s="8">
+        <v>24524</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="E86" s="19">
-        <v>406.0</v>
-      </c>
-      <c r="F86" s="20" t="s">
+      <c r="E86" s="10">
+        <v>406</v>
+      </c>
+      <c r="F86" s="11" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="87" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A87" s="13" t="s">
+    <row r="87" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A87" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F87" s="20"/>
-    </row>
-    <row r="88" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A88" s="13" t="s">
+      <c r="B87" s="15"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" s="11"/>
+    </row>
+    <row r="88" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A88" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F88" s="20"/>
-    </row>
-    <row r="89" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A89" s="16" t="s">
+      <c r="B88" s="15"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88" s="11"/>
+    </row>
+    <row r="89" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A89" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C89" s="17">
-        <v>23761.0</v>
-      </c>
-      <c r="D89" s="18" t="s">
+      <c r="C89" s="8">
+        <v>23761</v>
+      </c>
+      <c r="D89" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E89" s="19" t="s">
+      <c r="E89" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F89" s="20" t="s">
+      <c r="F89" s="11" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="90" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A90" s="13" t="s">
+    <row r="90" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A90" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E90" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F90" s="20"/>
-    </row>
-    <row r="91" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A91" s="16" t="s">
+      <c r="B90" s="15"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90" s="11"/>
+    </row>
+    <row r="91" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A91" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C91" s="17">
-        <v>26360.0</v>
-      </c>
-      <c r="D91" s="18" t="s">
+      <c r="C91" s="8">
+        <v>26360</v>
+      </c>
+      <c r="D91" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E91" s="19">
-        <v>406.0</v>
-      </c>
-      <c r="F91" s="20" t="s">
+      <c r="E91" s="10">
+        <v>406</v>
+      </c>
+      <c r="F91" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="92" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A92" s="13" t="s">
+    <row r="92" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A92" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E92" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F92" s="20"/>
-    </row>
-    <row r="93" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A93" s="13" t="s">
+      <c r="B92" s="15"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F92" s="11"/>
+    </row>
+    <row r="93" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A93" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E93" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F93" s="20"/>
-    </row>
-    <row r="94" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A94" s="16" t="s">
+      <c r="B93" s="15"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93" s="11"/>
+    </row>
+    <row r="94" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A94" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B94" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C94" s="17">
-        <v>28209.0</v>
-      </c>
-      <c r="D94" s="18" t="s">
+      <c r="C94" s="8">
+        <v>28209</v>
+      </c>
+      <c r="D94" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="E94" s="19">
-        <v>404.0</v>
-      </c>
-      <c r="F94" s="20" t="s">
+      <c r="E94" s="10">
+        <v>404</v>
+      </c>
+      <c r="F94" s="11" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="95" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A95" s="16" t="s">
+    <row r="95" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A95" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B95" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C95" s="17">
-        <v>23874.0</v>
-      </c>
-      <c r="D95" s="18" t="s">
+      <c r="C95" s="8">
+        <v>23874</v>
+      </c>
+      <c r="D95" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E95" s="19">
-        <v>404.0</v>
-      </c>
-      <c r="F95" s="20" t="s">
+      <c r="E95" s="10">
+        <v>404</v>
+      </c>
+      <c r="F95" s="11" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="96" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A96" s="13" t="s">
+    <row r="96" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A96" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="B96" s="5"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E96" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F96" s="20"/>
-    </row>
-    <row r="97" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A97" s="16" t="s">
+      <c r="B96" s="15"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96" s="11"/>
+    </row>
+    <row r="97" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A97" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B97" s="16" t="s">
+      <c r="B97" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C97" s="17">
-        <v>29164.0</v>
-      </c>
-      <c r="D97" s="18" t="s">
+      <c r="C97" s="8">
+        <v>29164</v>
+      </c>
+      <c r="D97" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E97" s="19" t="s">
+      <c r="E97" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F97" s="20" t="s">
+      <c r="F97" s="11" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="98" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A98" s="16" t="s">
+    <row r="98" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A98" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B98" s="16" t="s">
+      <c r="B98" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="C98" s="17">
-        <v>24613.0</v>
-      </c>
-      <c r="D98" s="18" t="s">
+      <c r="C98" s="8">
+        <v>24613</v>
+      </c>
+      <c r="D98" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="E98" s="19" t="s">
+      <c r="E98" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F98" s="20" t="s">
+      <c r="F98" s="11" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="99" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A99" s="16" t="s">
+    <row r="99" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A99" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B99" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C99" s="17">
-        <v>30619.0</v>
-      </c>
-      <c r="D99" s="18" t="s">
+      <c r="C99" s="8">
+        <v>30619</v>
+      </c>
+      <c r="D99" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="E99" s="19" t="s">
+      <c r="E99" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F99" s="20" t="s">
+      <c r="F99" s="11" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="100" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A100" s="13" t="s">
+    <row r="100" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A100" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="B100" s="5"/>
-      <c r="C100" s="17"/>
-      <c r="D100" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E100" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F100" s="20"/>
-    </row>
-    <row r="101" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A101" s="16" t="s">
+      <c r="B100" s="15"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F100" s="11"/>
+    </row>
+    <row r="101" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A101" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B101" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C101" s="17">
-        <v>29358.0</v>
-      </c>
-      <c r="D101" s="18" t="s">
+      <c r="C101" s="8">
+        <v>29358</v>
+      </c>
+      <c r="D101" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="E101" s="19" t="s">
+      <c r="E101" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F101" s="20" t="s">
+      <c r="F101" s="11" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="102" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A102" s="13" t="s">
+    <row r="102" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="B102" s="5"/>
-      <c r="C102" s="17"/>
-      <c r="D102" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E102" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F102" s="20"/>
-    </row>
-    <row r="103" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A103" s="13" t="s">
+      <c r="B102" s="25"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F102" s="11"/>
+    </row>
+    <row r="103" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A103" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="B103" s="5"/>
-      <c r="C103" s="17"/>
-      <c r="D103" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E103" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F103" s="20"/>
-    </row>
-    <row r="104" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A104" s="16" t="s">
+      <c r="B103" s="15"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F103" s="11"/>
+    </row>
+    <row r="104" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A104" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B104" s="16" t="s">
+      <c r="B104" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C104" s="17">
-        <v>37349.0</v>
-      </c>
-      <c r="D104" s="18" t="s">
+      <c r="C104" s="8">
+        <v>37349</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E104" s="19">
-        <v>406.0</v>
-      </c>
-      <c r="F104" s="20" t="s">
+      <c r="E104" s="10">
+        <v>406</v>
+      </c>
+      <c r="F104" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="105" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A105" s="13" t="s">
+    <row r="105" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A105" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="B105" s="5"/>
-      <c r="C105" s="17"/>
-      <c r="D105" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E105" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F105" s="20"/>
-    </row>
-    <row r="106" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A106" s="13" t="s">
+      <c r="B105" s="15"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F105" s="11"/>
+    </row>
+    <row r="106" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A106" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="B106" s="5"/>
-      <c r="C106" s="17"/>
-      <c r="D106" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E106" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F106" s="20"/>
-    </row>
-    <row r="107" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A107" s="16" t="s">
+      <c r="B106" s="15"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F106" s="11"/>
+    </row>
+    <row r="107" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A107" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="C107" s="17">
-        <v>23920.0</v>
-      </c>
-      <c r="D107" s="18" t="s">
+      <c r="C107" s="8">
+        <v>23920</v>
+      </c>
+      <c r="D107" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="E107" s="19" t="s">
+      <c r="E107" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F107" s="20" t="s">
+      <c r="F107" s="11" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="108" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A108" s="13" t="s">
+    <row r="108" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A108" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="17"/>
-      <c r="D108" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E108" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F108" s="20"/>
-    </row>
-    <row r="109" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A109" s="16" t="s">
+      <c r="B108" s="15"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F108" s="11"/>
+    </row>
+    <row r="109" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A109" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B109" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C109" s="17">
-        <v>23735.0</v>
-      </c>
-      <c r="D109" s="18" t="s">
+      <c r="C109" s="8">
+        <v>23735</v>
+      </c>
+      <c r="D109" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="E109" s="19" t="s">
+      <c r="E109" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="F109" s="20" t="s">
+      <c r="F109" s="11" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="110" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A110" s="13" t="s">
+    <row r="110" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A110" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="B110" s="5"/>
-      <c r="C110" s="17"/>
-      <c r="D110" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E110" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F110" s="20"/>
-    </row>
-    <row r="111" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A111" s="13" t="s">
+      <c r="B110" s="15"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F110" s="11"/>
+    </row>
+    <row r="111" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A111" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="B111" s="5"/>
-      <c r="C111" s="17"/>
-      <c r="D111" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E111" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F111" s="20"/>
-    </row>
-    <row r="112" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A112" s="16" t="s">
+      <c r="B111" s="15"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111" s="11"/>
+    </row>
+    <row r="112" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A112" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B112" s="16" t="s">
+      <c r="B112" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C112" s="17">
-        <v>28343.0</v>
-      </c>
-      <c r="D112" s="18" t="s">
+      <c r="C112" s="8">
+        <v>28343</v>
+      </c>
+      <c r="D112" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="E112" s="19" t="s">
+      <c r="E112" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F112" s="20" t="s">
+      <c r="F112" s="11" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="113" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A113" s="16" t="s">
+    <row r="113" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A113" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B113" s="16" t="s">
+      <c r="B113" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="C113" s="17">
-        <v>30526.0</v>
-      </c>
-      <c r="D113" s="18" t="s">
+      <c r="C113" s="8">
+        <v>30526</v>
+      </c>
+      <c r="D113" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="E113" s="19" t="s">
+      <c r="E113" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F113" s="20" t="s">
+      <c r="F113" s="11" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="114" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A114" s="16" t="s">
+    <row r="114" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A114" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B114" s="16" t="s">
+      <c r="B114" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C114" s="17">
-        <v>32441.0</v>
-      </c>
-      <c r="D114" s="18" t="s">
+      <c r="C114" s="8">
+        <v>32441</v>
+      </c>
+      <c r="D114" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="E114" s="19" t="s">
+      <c r="E114" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F114" s="20" t="s">
+      <c r="F114" s="11" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="115" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A115" s="13" t="s">
+    <row r="115" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A115" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="B115" s="5"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E115" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F115" s="20"/>
-    </row>
-    <row r="116" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A116" s="16" t="s">
+      <c r="B115" s="15"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F115" s="11"/>
+    </row>
+    <row r="116" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A116" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B116" s="16" t="s">
+      <c r="B116" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C116" s="17">
-        <v>34165.0</v>
-      </c>
-      <c r="D116" s="18" t="s">
+      <c r="C116" s="8">
+        <v>34165</v>
+      </c>
+      <c r="D116" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="E116" s="19" t="s">
+      <c r="E116" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="F116" s="20" t="s">
+      <c r="F116" s="11" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="117" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A117" s="13" t="s">
+    <row r="117" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A117" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="17"/>
-      <c r="D117" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E117" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F117" s="20"/>
-    </row>
-    <row r="118" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A118" s="16" t="s">
+      <c r="B117" s="15"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F117" s="11"/>
+    </row>
+    <row r="118" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A118" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B118" s="16" t="s">
+      <c r="B118" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="C118" s="17">
-        <v>32961.0</v>
-      </c>
-      <c r="D118" s="18" t="s">
+      <c r="C118" s="8">
+        <v>32961</v>
+      </c>
+      <c r="D118" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="E118" s="19">
-        <v>411.0</v>
-      </c>
-      <c r="F118" s="20" t="s">
+      <c r="E118" s="10">
+        <v>411</v>
+      </c>
+      <c r="F118" s="11" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="119" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A119" s="16" t="s">
+    <row r="119" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A119" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B119" s="16" t="s">
+      <c r="B119" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C119" s="17">
-        <v>24652.0</v>
-      </c>
-      <c r="D119" s="18" t="s">
+      <c r="C119" s="8">
+        <v>24652</v>
+      </c>
+      <c r="D119" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E119" s="19">
-        <v>411.0</v>
-      </c>
-      <c r="F119" s="20" t="s">
+      <c r="E119" s="10">
+        <v>411</v>
+      </c>
+      <c r="F119" s="11" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="120" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A120" s="13" t="s">
+    <row r="120" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="B120" s="5"/>
-      <c r="C120" s="17"/>
-      <c r="D120" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F120" s="20"/>
-    </row>
-    <row r="121" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A121" s="16" t="s">
+      <c r="B120" s="25"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F120" s="11"/>
+    </row>
+    <row r="121" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A121" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B121" s="16" t="s">
+      <c r="B121" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="C121" s="17">
-        <v>27498.0</v>
-      </c>
-      <c r="D121" s="18" t="s">
+      <c r="C121" s="8">
+        <v>27498</v>
+      </c>
+      <c r="D121" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="E121" s="19" t="s">
+      <c r="E121" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="F121" s="20" t="s">
+      <c r="F121" s="11" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="122" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A122" s="16" t="s">
+    <row r="122" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A122" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B122" s="16" t="s">
+      <c r="B122" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C122" s="17">
-        <v>22357.0</v>
-      </c>
-      <c r="D122" s="18" t="s">
+      <c r="C122" s="8">
+        <v>22357</v>
+      </c>
+      <c r="D122" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="E122" s="19" t="s">
+      <c r="E122" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="F122" s="20" t="s">
+      <c r="F122" s="11" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="123" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A123" s="16" t="s">
+    <row r="123" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A123" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B123" s="16" t="s">
+      <c r="B123" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="C123" s="17">
-        <v>25491.0</v>
-      </c>
-      <c r="D123" s="18" t="s">
+      <c r="C123" s="8">
+        <v>25491</v>
+      </c>
+      <c r="D123" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="E123" s="19" t="s">
+      <c r="E123" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="F123" s="20" t="s">
+      <c r="F123" s="11" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="124" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A124" s="13" t="s">
+    <row r="124" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="24" t="s">
         <v>322</v>
       </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="17"/>
-      <c r="D124" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E124" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F124" s="20"/>
-    </row>
-    <row r="125" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A125" s="16" t="s">
+      <c r="B124" s="25"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F124" s="11"/>
+    </row>
+    <row r="125" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A125" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B125" s="16" t="s">
+      <c r="B125" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C125" s="17">
-        <v>24160.0</v>
-      </c>
-      <c r="D125" s="18" t="s">
+      <c r="C125" s="8">
+        <v>24160</v>
+      </c>
+      <c r="D125" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E125" s="19">
-        <v>401.0</v>
-      </c>
-      <c r="F125" s="20" t="s">
+      <c r="E125" s="10">
+        <v>401</v>
+      </c>
+      <c r="F125" s="11" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="126" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A126" s="16" t="s">
+    <row r="126" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A126" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B126" s="16" t="s">
+      <c r="B126" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C126" s="17">
-        <v>28946.0</v>
-      </c>
-      <c r="D126" s="18" t="s">
+      <c r="C126" s="8">
+        <v>28946</v>
+      </c>
+      <c r="D126" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="E126" s="19">
-        <v>401.0</v>
-      </c>
-      <c r="F126" s="20" t="s">
+      <c r="E126" s="10">
+        <v>401</v>
+      </c>
+      <c r="F126" s="11" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="127" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A127" s="16" t="s">
+    <row r="127" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A127" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B127" s="16" t="s">
+      <c r="B127" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="C127" s="17">
-        <v>30500.0</v>
-      </c>
-      <c r="D127" s="18" t="s">
+      <c r="C127" s="8">
+        <v>30500</v>
+      </c>
+      <c r="D127" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E127" s="19">
-        <v>401.0</v>
-      </c>
-      <c r="F127" s="20" t="s">
+      <c r="E127" s="10">
+        <v>401</v>
+      </c>
+      <c r="F127" s="11" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="128" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A128" s="16" t="s">
+    <row r="128" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A128" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="B128" s="16" t="s">
+      <c r="B128" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="C128" s="17">
-        <v>26081.0</v>
-      </c>
-      <c r="D128" s="18" t="s">
+      <c r="C128" s="8">
+        <v>26081</v>
+      </c>
+      <c r="D128" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="E128" s="19">
-        <v>401.0</v>
-      </c>
-      <c r="F128" s="20" t="s">
+      <c r="E128" s="10">
+        <v>401</v>
+      </c>
+      <c r="F128" s="11" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="129" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A129" s="13" t="s">
+    <row r="129" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="24" t="s">
         <v>335</v>
       </c>
-      <c r="B129" s="5"/>
-      <c r="C129" s="17"/>
-      <c r="D129" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E129" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F129" s="20"/>
-    </row>
-    <row r="130" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A130" s="16" t="s">
+      <c r="B129" s="25"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F129" s="11"/>
+    </row>
+    <row r="130" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A130" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B130" s="16" t="s">
+      <c r="B130" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="C130" s="17">
-        <v>31440.0</v>
-      </c>
-      <c r="D130" s="18" t="s">
+      <c r="C130" s="8">
+        <v>31440</v>
+      </c>
+      <c r="D130" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="E130" s="19" t="s">
+      <c r="E130" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F130" s="20" t="s">
+      <c r="F130" s="11" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="131" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A131" s="16" t="s">
+    <row r="131" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A131" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B131" s="16" t="s">
+      <c r="B131" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="C131" s="17">
-        <v>23827.0</v>
-      </c>
-      <c r="D131" s="18" t="s">
+      <c r="C131" s="8">
+        <v>23827</v>
+      </c>
+      <c r="D131" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="E131" s="19" t="s">
+      <c r="E131" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F131" s="20" t="s">
+      <c r="F131" s="11" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="132" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A132" s="16" t="s">
+    <row r="132" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A132" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B132" s="16" t="s">
+      <c r="B132" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C132" s="17">
-        <v>22279.0</v>
-      </c>
-      <c r="D132" s="18" t="s">
+      <c r="C132" s="8">
+        <v>22279</v>
+      </c>
+      <c r="D132" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="E132" s="19" t="s">
+      <c r="E132" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F132" s="20" t="s">
+      <c r="F132" s="11" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="133" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A133" s="16" t="s">
+    <row r="133" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A133" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B133" s="16" t="s">
+      <c r="B133" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="C133" s="17">
-        <v>22896.0</v>
-      </c>
-      <c r="D133" s="18" t="s">
+      <c r="C133" s="8">
+        <v>22896</v>
+      </c>
+      <c r="D133" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="E133" s="19" t="s">
+      <c r="E133" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F133" s="20" t="s">
+      <c r="F133" s="11" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="134" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A134" s="16" t="s">
+    <row r="134" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A134" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B134" s="16" t="s">
+      <c r="B134" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="C134" s="17">
-        <v>27320.0</v>
-      </c>
-      <c r="D134" s="18" t="s">
+      <c r="C134" s="8">
+        <v>27320</v>
+      </c>
+      <c r="D134" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="E134" s="19" t="s">
+      <c r="E134" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="F134" s="20" t="s">
+      <c r="F134" s="11" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="135" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A135" s="13" t="s">
+    <row r="135" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="24" t="s">
         <v>350</v>
       </c>
-      <c r="B135" s="5"/>
-      <c r="C135" s="17"/>
-      <c r="D135" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E135" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F135" s="20"/>
-    </row>
-    <row r="136" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A136" s="13" t="s">
+      <c r="B135" s="25"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F135" s="11"/>
+    </row>
+    <row r="136" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A136" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B136" s="5"/>
-      <c r="C136" s="17"/>
-      <c r="D136" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E136" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F136" s="20"/>
-    </row>
-    <row r="137" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A137" s="16" t="s">
+      <c r="B136" s="15"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F136" s="11"/>
+    </row>
+    <row r="137" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A137" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B137" s="16" t="s">
+      <c r="B137" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C137" s="17">
-        <v>30313.0</v>
-      </c>
-      <c r="D137" s="18" t="s">
+      <c r="C137" s="8">
+        <v>30313</v>
+      </c>
+      <c r="D137" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="E137" s="19">
-        <v>487.0</v>
-      </c>
-      <c r="F137" s="20" t="s">
+      <c r="E137" s="10">
+        <v>487</v>
+      </c>
+      <c r="F137" s="11" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="138" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A138" s="16" t="s">
+    <row r="138" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A138" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B138" s="16" t="s">
+      <c r="B138" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C138" s="17">
-        <v>28283.0</v>
-      </c>
-      <c r="D138" s="18" t="s">
+      <c r="C138" s="8">
+        <v>28283</v>
+      </c>
+      <c r="D138" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="E138" s="19">
-        <v>487.0</v>
-      </c>
-      <c r="F138" s="20" t="s">
+      <c r="E138" s="10">
+        <v>487</v>
+      </c>
+      <c r="F138" s="11" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="139" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A139" s="16" t="s">
+    <row r="139" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A139" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B139" s="16" t="s">
+      <c r="B139" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="C139" s="17">
-        <v>28852.0</v>
-      </c>
-      <c r="D139" s="18" t="s">
+      <c r="C139" s="8">
+        <v>28852</v>
+      </c>
+      <c r="D139" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="E139" s="19">
-        <v>487.0</v>
-      </c>
-      <c r="F139" s="20" t="s">
+      <c r="E139" s="10">
+        <v>487</v>
+      </c>
+      <c r="F139" s="11" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="140" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A140" s="13" t="s">
+    <row r="140" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A140" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="B140" s="5"/>
-      <c r="C140" s="17"/>
-      <c r="D140" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E140" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F140" s="20"/>
-    </row>
-    <row r="141" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A141" s="16" t="s">
+      <c r="B140" s="15"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F140" s="11"/>
+    </row>
+    <row r="141" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A141" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B141" s="16" t="s">
+      <c r="B141" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="C141" s="17">
-        <v>31825.0</v>
-      </c>
-      <c r="D141" s="18" t="s">
+      <c r="C141" s="8">
+        <v>31825</v>
+      </c>
+      <c r="D141" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="E141" s="19">
-        <v>421.0</v>
-      </c>
-      <c r="F141" s="20" t="s">
+      <c r="E141" s="10">
+        <v>421</v>
+      </c>
+      <c r="F141" s="11" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="142" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A142" s="16" t="s">
+    <row r="142" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A142" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B142" s="16" t="s">
+      <c r="B142" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="C142" s="17">
-        <v>29199.0</v>
-      </c>
-      <c r="D142" s="18" t="s">
+      <c r="C142" s="8">
+        <v>29199</v>
+      </c>
+      <c r="D142" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="E142" s="19">
-        <v>421.0</v>
-      </c>
-      <c r="F142" s="20" t="s">
+      <c r="E142" s="10">
+        <v>421</v>
+      </c>
+      <c r="F142" s="11" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="143" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A143" s="13" t="s">
+    <row r="143" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="24" t="s">
         <v>367</v>
       </c>
-      <c r="B143" s="5"/>
-      <c r="C143" s="17"/>
-      <c r="D143" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E143" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F143" s="20"/>
-    </row>
-    <row r="144" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A144" s="16" t="s">
+      <c r="B143" s="25"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F143" s="11"/>
+    </row>
+    <row r="144" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A144" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B144" s="16" t="s">
+      <c r="B144" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="C144" s="17">
-        <v>34879.0</v>
-      </c>
-      <c r="D144" s="18" t="s">
+      <c r="C144" s="8">
+        <v>34879</v>
+      </c>
+      <c r="D144" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="E144" s="19">
-        <v>401.0</v>
-      </c>
-      <c r="F144" s="20" t="s">
+      <c r="E144" s="10">
+        <v>401</v>
+      </c>
+      <c r="F144" s="11" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="145" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A145" s="16" t="s">
+    <row r="145" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A145" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B145" s="16" t="s">
+      <c r="B145" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="C145" s="17">
-        <v>32536.0</v>
-      </c>
-      <c r="D145" s="18" t="s">
+      <c r="C145" s="8">
+        <v>32536</v>
+      </c>
+      <c r="D145" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="E145" s="19">
-        <v>401.0</v>
-      </c>
-      <c r="F145" s="20" t="s">
+      <c r="E145" s="10">
+        <v>401</v>
+      </c>
+      <c r="F145" s="11" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="146" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A146" s="16" t="s">
+    <row r="146" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A146" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B146" s="16" t="s">
+      <c r="B146" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="C146" s="17">
-        <v>36475.0</v>
-      </c>
-      <c r="D146" s="18" t="s">
+      <c r="C146" s="8">
+        <v>36475</v>
+      </c>
+      <c r="D146" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="E146" s="19">
-        <v>401.0</v>
-      </c>
-      <c r="F146" s="20" t="s">
+      <c r="E146" s="10">
+        <v>401</v>
+      </c>
+      <c r="F146" s="11" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="147" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A147" s="16" t="s">
+    <row r="147" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A147" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B147" s="16" t="s">
+      <c r="B147" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="C147" s="17">
-        <v>24721.0</v>
-      </c>
-      <c r="D147" s="18" t="s">
+      <c r="C147" s="8">
+        <v>24721</v>
+      </c>
+      <c r="D147" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="E147" s="19">
-        <v>401.0</v>
-      </c>
-      <c r="F147" s="20" t="s">
+      <c r="E147" s="10">
+        <v>401</v>
+      </c>
+      <c r="F147" s="11" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="148" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A148" s="13" t="s">
+    <row r="148" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="B148" s="5"/>
-      <c r="C148" s="17"/>
-      <c r="D148" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E148" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F148" s="20"/>
-    </row>
-    <row r="149" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A149" s="13" t="s">
+      <c r="B148" s="25"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F148" s="11"/>
+    </row>
+    <row r="149" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A149" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="B149" s="5"/>
-      <c r="C149" s="17"/>
-      <c r="D149" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E149" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F149" s="20"/>
-    </row>
-    <row r="150" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A150" s="16" t="s">
+      <c r="B149" s="15"/>
+      <c r="C149" s="8"/>
+      <c r="D149" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F149" s="11"/>
+    </row>
+    <row r="150" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A150" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B150" s="16" t="s">
+      <c r="B150" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="17">
-        <v>25505.0</v>
-      </c>
-      <c r="D150" s="18" t="s">
+      <c r="C150" s="8">
+        <v>25505</v>
+      </c>
+      <c r="D150" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="E150" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F150" s="20" t="s">
+      <c r="E150" s="10">
+        <v>488</v>
+      </c>
+      <c r="F150" s="11" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="151" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A151" s="16" t="s">
+    <row r="151" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A151" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B151" s="16" t="s">
+      <c r="B151" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="C151" s="17">
-        <v>35578.0</v>
-      </c>
-      <c r="D151" s="18" t="s">
+      <c r="C151" s="8">
+        <v>35578</v>
+      </c>
+      <c r="D151" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="E151" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F151" s="20" t="s">
+      <c r="E151" s="10">
+        <v>488</v>
+      </c>
+      <c r="F151" s="11" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="152" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A152" s="16" t="s">
+    <row r="152" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A152" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B152" s="16" t="s">
+      <c r="B152" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="C152" s="17">
-        <v>22106.0</v>
-      </c>
-      <c r="D152" s="18" t="s">
+      <c r="C152" s="8">
+        <v>22106</v>
+      </c>
+      <c r="D152" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="E152" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F152" s="20" t="s">
+      <c r="E152" s="10">
+        <v>488</v>
+      </c>
+      <c r="F152" s="11" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="153" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A153" s="16" t="s">
+    <row r="153" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A153" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="B153" s="16" t="s">
+      <c r="B153" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="C153" s="17">
-        <v>25555.0</v>
-      </c>
-      <c r="D153" s="18" t="s">
+      <c r="C153" s="8">
+        <v>25555</v>
+      </c>
+      <c r="D153" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="E153" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F153" s="20" t="s">
+      <c r="E153" s="10">
+        <v>488</v>
+      </c>
+      <c r="F153" s="11" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="154" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A154" s="16" t="s">
+    <row r="154" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A154" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="B154" s="16" t="s">
+      <c r="B154" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="C154" s="17">
-        <v>33728.0</v>
-      </c>
-      <c r="D154" s="18" t="s">
+      <c r="C154" s="8">
+        <v>33728</v>
+      </c>
+      <c r="D154" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="E154" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F154" s="20" t="s">
+      <c r="E154" s="10">
+        <v>488</v>
+      </c>
+      <c r="F154" s="11" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="155" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A155" s="16" t="s">
+    <row r="155" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A155" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="B155" s="16" t="s">
+      <c r="B155" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="C155" s="21">
-        <v>30469.0</v>
-      </c>
-      <c r="D155" s="18" t="s">
+      <c r="C155" s="12">
+        <v>30469</v>
+      </c>
+      <c r="D155" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="E155" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F155" s="20" t="s">
+      <c r="E155" s="10">
+        <v>488</v>
+      </c>
+      <c r="F155" s="11" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="156" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A156" s="16" t="s">
+    <row r="156" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A156" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B156" s="16" t="s">
+      <c r="B156" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C156" s="17">
-        <v>22946.0</v>
-      </c>
-      <c r="D156" s="18" t="s">
+      <c r="C156" s="8">
+        <v>22946</v>
+      </c>
+      <c r="D156" s="9" t="s">
         <v>405</v>
       </c>
-      <c r="E156" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F156" s="20" t="s">
+      <c r="E156" s="10">
+        <v>488</v>
+      </c>
+      <c r="F156" s="11" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="157" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A157" s="16" t="s">
+    <row r="157" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A157" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="B157" s="16" t="s">
+      <c r="B157" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="C157" s="17">
-        <v>27119.0</v>
-      </c>
-      <c r="D157" s="18" t="s">
+      <c r="C157" s="8">
+        <v>27119</v>
+      </c>
+      <c r="D157" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="E157" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F157" s="20" t="s">
+      <c r="E157" s="10">
+        <v>488</v>
+      </c>
+      <c r="F157" s="11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="158" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A158" s="16" t="s">
+    <row r="158" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A158" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="B158" s="16" t="s">
+      <c r="B158" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="C158" s="17">
-        <v>24551.0</v>
-      </c>
-      <c r="D158" s="18" t="s">
+      <c r="C158" s="8">
+        <v>24551</v>
+      </c>
+      <c r="D158" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="E158" s="19">
-        <v>488.0</v>
-      </c>
-      <c r="F158" s="20" t="s">
+      <c r="E158" s="10">
+        <v>488</v>
+      </c>
+      <c r="F158" s="11" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="159" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A159" s="13" t="s">
+    <row r="159" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A159" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="B159" s="5"/>
-      <c r="C159" s="17"/>
-      <c r="D159" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E159" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F159" s="20"/>
-    </row>
-    <row r="160" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A160" s="13" t="s">
+      <c r="B159" s="15"/>
+      <c r="C159" s="8"/>
+      <c r="D159" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F159" s="11"/>
+    </row>
+    <row r="160" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A160" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="B160" s="5"/>
-      <c r="C160" s="17"/>
-      <c r="D160" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E160" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F160" s="20"/>
-    </row>
-    <row r="161" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A161" s="16" t="s">
+      <c r="B160" s="15"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F160" s="11"/>
+    </row>
+    <row r="161" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A161" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B161" s="16" t="s">
+      <c r="B161" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="C161" s="17">
-        <v>26492.0</v>
-      </c>
-      <c r="D161" s="18" t="s">
+      <c r="C161" s="8">
+        <v>26492</v>
+      </c>
+      <c r="D161" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="E161" s="19">
-        <v>421.0</v>
-      </c>
-      <c r="F161" s="20" t="s">
+      <c r="E161" s="10">
+        <v>421</v>
+      </c>
+      <c r="F161" s="11" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="162" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A162" s="16" t="s">
+    <row r="162" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A162" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B162" s="16" t="s">
+      <c r="B162" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="C162" s="17">
-        <v>23839.0</v>
-      </c>
-      <c r="D162" s="18" t="s">
+      <c r="C162" s="8">
+        <v>23839</v>
+      </c>
+      <c r="D162" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="E162" s="19">
-        <v>421.0</v>
-      </c>
-      <c r="F162" s="20" t="s">
+      <c r="E162" s="10">
+        <v>421</v>
+      </c>
+      <c r="F162" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="163" ht="10.5" customHeight="1" outlineLevel="4">
-      <c r="A163" s="16" t="s">
+    <row r="163" spans="1:6" ht="10.5" customHeight="1" outlineLevel="4" x14ac:dyDescent="0.2">
+      <c r="A163" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B163" s="16" t="s">
+      <c r="B163" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="C163" s="17">
-        <v>32205.0</v>
-      </c>
-      <c r="D163" s="18" t="s">
+      <c r="C163" s="8">
+        <v>32205</v>
+      </c>
+      <c r="D163" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="E163" s="19">
-        <v>421.0</v>
-      </c>
-      <c r="F163" s="20" t="s">
+      <c r="E163" s="10">
+        <v>421</v>
+      </c>
+      <c r="F163" s="11" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="164" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A164" s="13" t="s">
+    <row r="164" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A164" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="B164" s="5"/>
-      <c r="C164" s="17"/>
-      <c r="D164" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E164" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F164" s="20"/>
-    </row>
-    <row r="165" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A165" s="16" t="s">
+      <c r="B164" s="15"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F164" s="11"/>
+    </row>
+    <row r="165" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A165" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B165" s="16" t="s">
+      <c r="B165" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="C165" s="17">
-        <v>25344.0</v>
-      </c>
-      <c r="D165" s="18" t="s">
+      <c r="C165" s="8">
+        <v>25344</v>
+      </c>
+      <c r="D165" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="E165" s="19">
-        <v>524.0</v>
-      </c>
-      <c r="F165" s="20" t="s">
+      <c r="E165" s="10">
+        <v>524</v>
+      </c>
+      <c r="F165" s="11" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="166" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A166" s="16" t="s">
+    <row r="166" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A166" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="B166" s="16" t="s">
+      <c r="B166" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="C166" s="17">
-        <v>24872.0</v>
-      </c>
-      <c r="D166" s="18" t="s">
+      <c r="C166" s="8">
+        <v>24872</v>
+      </c>
+      <c r="D166" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="E166" s="19">
-        <v>524.0</v>
-      </c>
-      <c r="F166" s="20" t="s">
+      <c r="E166" s="10">
+        <v>524</v>
+      </c>
+      <c r="F166" s="11" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="167" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A167" s="16" t="s">
+    <row r="167" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A167" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B167" s="16" t="s">
+      <c r="B167" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="C167" s="17">
-        <v>30554.0</v>
-      </c>
-      <c r="D167" s="18" t="s">
+      <c r="C167" s="8">
+        <v>30554</v>
+      </c>
+      <c r="D167" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="E167" s="19">
-        <v>524.0</v>
-      </c>
-      <c r="F167" s="20" t="s">
+      <c r="E167" s="10">
+        <v>524</v>
+      </c>
+      <c r="F167" s="11" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="168" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A168" s="16" t="s">
+    <row r="168" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A168" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="B168" s="16" t="s">
+      <c r="B168" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="C168" s="17">
-        <v>37588.0</v>
-      </c>
-      <c r="D168" s="18" t="s">
+      <c r="C168" s="8">
+        <v>37588</v>
+      </c>
+      <c r="D168" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="E168" s="19">
-        <v>524.0</v>
-      </c>
-      <c r="F168" s="20" t="s">
+      <c r="E168" s="10">
+        <v>524</v>
+      </c>
+      <c r="F168" s="11" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="169" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A169" s="13" t="s">
+    <row r="169" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A169" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="B169" s="5"/>
-      <c r="C169" s="17"/>
-      <c r="D169" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E169" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F169" s="20"/>
-    </row>
-    <row r="170" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A170" s="16" t="s">
+      <c r="B169" s="15"/>
+      <c r="C169" s="8"/>
+      <c r="D169" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E169" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F169" s="11"/>
+    </row>
+    <row r="170" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A170" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="B170" s="16" t="s">
+      <c r="B170" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="C170" s="17">
-        <v>29368.0</v>
-      </c>
-      <c r="D170" s="18" t="s">
+      <c r="C170" s="8">
+        <v>29368</v>
+      </c>
+      <c r="D170" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="E170" s="19">
-        <v>523.0</v>
-      </c>
-      <c r="F170" s="20" t="s">
+      <c r="E170" s="10">
+        <v>523</v>
+      </c>
+      <c r="F170" s="11" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="171" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A171" s="16" t="s">
+    <row r="171" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A171" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B171" s="16" t="s">
+      <c r="B171" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="C171" s="17">
-        <v>31276.0</v>
-      </c>
-      <c r="D171" s="18" t="s">
+      <c r="C171" s="8">
+        <v>31276</v>
+      </c>
+      <c r="D171" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="E171" s="19">
-        <v>523.0</v>
-      </c>
-      <c r="F171" s="20" t="s">
+      <c r="E171" s="10">
+        <v>523</v>
+      </c>
+      <c r="F171" s="11" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="172" ht="10.5" customHeight="1" outlineLevel="1">
-      <c r="A172" s="13" t="s">
+    <row r="172" spans="1:6" ht="10.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="24" t="s">
         <v>442</v>
       </c>
-      <c r="B172" s="5"/>
-      <c r="C172" s="17"/>
-      <c r="D172" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E172" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F172" s="20"/>
-    </row>
-    <row r="173" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A173" s="13" t="s">
+      <c r="B172" s="25"/>
+      <c r="C172" s="8"/>
+      <c r="D172" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F172" s="11"/>
+    </row>
+    <row r="173" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A173" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="B173" s="5"/>
-      <c r="C173" s="17"/>
-      <c r="D173" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E173" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F173" s="20"/>
-    </row>
-    <row r="174" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A174" s="16" t="s">
+      <c r="B173" s="15"/>
+      <c r="C173" s="8"/>
+      <c r="D173" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E173" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F173" s="11"/>
+    </row>
+    <row r="174" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A174" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B174" s="16" t="s">
+      <c r="B174" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="C174" s="17">
-        <v>35917.0</v>
-      </c>
-      <c r="D174" s="18" t="s">
+      <c r="C174" s="8">
+        <v>35917</v>
+      </c>
+      <c r="D174" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="E174" s="19">
-        <v>421.0</v>
-      </c>
-      <c r="F174" s="20" t="s">
+      <c r="E174" s="10">
+        <v>421</v>
+      </c>
+      <c r="F174" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="175" ht="10.5" customHeight="1" outlineLevel="2">
-      <c r="A175" s="13" t="s">
+    <row r="175" spans="1:6" ht="10.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A175" s="14" t="s">
         <v>446</v>
       </c>
-      <c r="B175" s="5"/>
-      <c r="C175" s="17"/>
-      <c r="D175" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E175" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F175" s="20"/>
-    </row>
-    <row r="176" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A176" s="16" t="s">
+      <c r="B175" s="15"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E175" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F175" s="11"/>
+    </row>
+    <row r="176" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A176" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B176" s="16" t="s">
+      <c r="B176" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="C176" s="17">
-        <v>27407.0</v>
-      </c>
-      <c r="D176" s="18" t="s">
+      <c r="C176" s="8">
+        <v>27407</v>
+      </c>
+      <c r="D176" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="E176" s="19">
-        <v>524.0</v>
-      </c>
-      <c r="F176" s="20" t="s">
+      <c r="E176" s="10">
+        <v>524</v>
+      </c>
+      <c r="F176" s="11" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="177" ht="10.5" customHeight="1" outlineLevel="3">
-      <c r="A177" s="16" t="s">
+    <row r="177" spans="1:6" ht="10.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.2">
+      <c r="A177" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B177" s="16" t="s">
+      <c r="B177" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="C177" s="17">
-        <v>33045.0</v>
-      </c>
-      <c r="D177" s="18" t="s">
+      <c r="C177" s="8">
+        <v>33045</v>
+      </c>
+      <c r="D177" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="E177" s="19">
-        <v>524.0</v>
-      </c>
-      <c r="F177" s="20" t="s">
+      <c r="E177" s="10">
+        <v>524</v>
+      </c>
+      <c r="F177" s="11" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="178" ht="12.75" customHeight="1">
-      <c r="A178" s="22" t="s">
+    <row r="178" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="B178" s="5"/>
-      <c r="C178" s="23"/>
-      <c r="D178" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E178" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F178" s="18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="179" ht="11.25" customHeight="1">
+      <c r="B178" s="15"/>
+      <c r="C178" s="13"/>
+      <c r="D178" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E178" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F178" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
     </row>
-    <row r="180" ht="11.25" customHeight="1">
+    <row r="180" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
     </row>
-    <row r="181" ht="11.25" customHeight="1">
+    <row r="181" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
     </row>
-    <row r="182" ht="11.25" customHeight="1">
+    <row r="182" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
     </row>
-    <row r="183" ht="11.25" customHeight="1">
+    <row r="183" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
     </row>
-    <row r="184" ht="11.25" customHeight="1">
+    <row r="184" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
     </row>
-    <row r="185" ht="11.25" customHeight="1">
+    <row r="185" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
     </row>
-    <row r="186" ht="11.25" customHeight="1">
+    <row r="186" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
     </row>
-    <row r="187" ht="11.25" customHeight="1">
+    <row r="187" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
     </row>
-    <row r="188" ht="11.25" customHeight="1">
+    <row r="188" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
     </row>
-    <row r="189" ht="11.25" customHeight="1">
+    <row r="189" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
     </row>
-    <row r="190" ht="11.25" customHeight="1">
+    <row r="190" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
     </row>
-    <row r="191" ht="11.25" customHeight="1">
+    <row r="191" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
     </row>
-    <row r="192" ht="11.25" customHeight="1">
+    <row r="192" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
     </row>
-    <row r="193" ht="11.25" customHeight="1">
+    <row r="193" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
     </row>
-    <row r="194" ht="11.25" customHeight="1">
+    <row r="194" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
     </row>
-    <row r="195" ht="11.25" customHeight="1">
+    <row r="195" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
     </row>
-    <row r="196" ht="11.25" customHeight="1">
+    <row r="196" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
     </row>
-    <row r="197" ht="11.25" customHeight="1">
+    <row r="197" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
     </row>
-    <row r="198" ht="11.25" customHeight="1">
+    <row r="198" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
     </row>
-    <row r="199" ht="11.25" customHeight="1">
+    <row r="199" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
     </row>
-    <row r="200" ht="11.25" customHeight="1">
+    <row r="200" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
     </row>
-    <row r="201" ht="11.25" customHeight="1">
+    <row r="201" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
     </row>
-    <row r="202" ht="11.25" customHeight="1">
+    <row r="202" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
     </row>
-    <row r="203" ht="11.25" customHeight="1">
+    <row r="203" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
     </row>
-    <row r="204" ht="11.25" customHeight="1">
+    <row r="204" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
     </row>
-    <row r="205" ht="11.25" customHeight="1">
+    <row r="205" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
     </row>
-    <row r="206" ht="11.25" customHeight="1">
+    <row r="206" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
     </row>
-    <row r="207" ht="11.25" customHeight="1">
+    <row r="207" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
     </row>
-    <row r="208" ht="11.25" customHeight="1">
+    <row r="208" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
     </row>
-    <row r="209" ht="11.25" customHeight="1">
+    <row r="209" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
     </row>
-    <row r="210" ht="11.25" customHeight="1">
+    <row r="210" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
     </row>
-    <row r="211" ht="11.25" customHeight="1">
+    <row r="211" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
     </row>
-    <row r="212" ht="11.25" customHeight="1">
+    <row r="212" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
     </row>
-    <row r="213" ht="11.25" customHeight="1">
+    <row r="213" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
     </row>
-    <row r="214" ht="11.25" customHeight="1">
+    <row r="214" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
     </row>
-    <row r="215" ht="11.25" customHeight="1">
+    <row r="215" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
     </row>
-    <row r="216" ht="11.25" customHeight="1">
+    <row r="216" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
     </row>
-    <row r="217" ht="11.25" customHeight="1">
+    <row r="217" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
     </row>
-    <row r="218" ht="11.25" customHeight="1">
+    <row r="218" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
     </row>
-    <row r="219" ht="11.25" customHeight="1">
+    <row r="219" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
     </row>
-    <row r="220" ht="11.25" customHeight="1">
+    <row r="220" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
     </row>
-    <row r="221" ht="11.25" customHeight="1">
+    <row r="221" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
     </row>
-    <row r="222" ht="11.25" customHeight="1">
+    <row r="222" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
     </row>
-    <row r="223" ht="11.25" customHeight="1">
+    <row r="223" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
     </row>
-    <row r="224" ht="11.25" customHeight="1">
+    <row r="224" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
     </row>
-    <row r="225" ht="11.25" customHeight="1">
+    <row r="225" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
     </row>
-    <row r="226" ht="11.25" customHeight="1">
+    <row r="226" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
     </row>
-    <row r="227" ht="11.25" customHeight="1">
+    <row r="227" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
     </row>
-    <row r="228" ht="11.25" customHeight="1">
+    <row r="228" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
     </row>
-    <row r="229" ht="11.25" customHeight="1">
+    <row r="229" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
     </row>
-    <row r="230" ht="11.25" customHeight="1">
+    <row r="230" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
     </row>
-    <row r="231" ht="11.25" customHeight="1">
+    <row r="231" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
     </row>
-    <row r="232" ht="11.25" customHeight="1">
+    <row r="232" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
     </row>
-    <row r="233" ht="11.25" customHeight="1">
+    <row r="233" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
     </row>
-    <row r="234" ht="11.25" customHeight="1">
+    <row r="234" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
     </row>
-    <row r="235" ht="11.25" customHeight="1">
+    <row r="235" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
     </row>
-    <row r="236" ht="11.25" customHeight="1">
+    <row r="236" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
     </row>
-    <row r="237" ht="11.25" customHeight="1">
+    <row r="237" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
     </row>
-    <row r="238" ht="11.25" customHeight="1">
+    <row r="238" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
     </row>
-    <row r="239" ht="11.25" customHeight="1">
+    <row r="239" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
     </row>
-    <row r="240" ht="11.25" customHeight="1">
+    <row r="240" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
     </row>
-    <row r="241" ht="11.25" customHeight="1">
+    <row r="241" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
     </row>
-    <row r="242" ht="11.25" customHeight="1">
+    <row r="242" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
     </row>
-    <row r="243" ht="11.25" customHeight="1">
+    <row r="243" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
     </row>
-    <row r="244" ht="11.25" customHeight="1">
+    <row r="244" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
     </row>
-    <row r="245" ht="11.25" customHeight="1">
+    <row r="245" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
     </row>
-    <row r="246" ht="11.25" customHeight="1">
+    <row r="246" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
     </row>
-    <row r="247" ht="11.25" customHeight="1">
+    <row r="247" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
     </row>
-    <row r="248" ht="11.25" customHeight="1">
+    <row r="248" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
     </row>
-    <row r="249" ht="11.25" customHeight="1">
+    <row r="249" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
     </row>
-    <row r="250" ht="11.25" customHeight="1">
+    <row r="250" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
     </row>
-    <row r="251" ht="11.25" customHeight="1">
+    <row r="251" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
     </row>
-    <row r="252" ht="11.25" customHeight="1">
+    <row r="252" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
     </row>
-    <row r="253" ht="11.25" customHeight="1">
+    <row r="253" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
     </row>
-    <row r="254" ht="11.25" customHeight="1">
+    <row r="254" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
     </row>
-    <row r="255" ht="11.25" customHeight="1">
+    <row r="255" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
     </row>
-    <row r="256" ht="11.25" customHeight="1">
+    <row r="256" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
     </row>
-    <row r="257" ht="11.25" customHeight="1">
+    <row r="257" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
     </row>
-    <row r="258" ht="11.25" customHeight="1">
+    <row r="258" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
     </row>
-    <row r="259" ht="11.25" customHeight="1">
+    <row r="259" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
     </row>
-    <row r="260" ht="11.25" customHeight="1">
+    <row r="260" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
     </row>
-    <row r="261" ht="11.25" customHeight="1">
+    <row r="261" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
     </row>
-    <row r="262" ht="11.25" customHeight="1">
+    <row r="262" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
     </row>
-    <row r="263" ht="11.25" customHeight="1">
+    <row r="263" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
     </row>
-    <row r="264" ht="11.25" customHeight="1">
+    <row r="264" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
     </row>
-    <row r="265" ht="11.25" customHeight="1">
+    <row r="265" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
     </row>
-    <row r="266" ht="11.25" customHeight="1">
+    <row r="266" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
     </row>
-    <row r="267" ht="11.25" customHeight="1">
+    <row r="267" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
     </row>
-    <row r="268" ht="11.25" customHeight="1">
+    <row r="268" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
     </row>
-    <row r="269" ht="11.25" customHeight="1">
+    <row r="269" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
     </row>
-    <row r="270" ht="11.25" customHeight="1">
+    <row r="270" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
     </row>
-    <row r="271" ht="11.25" customHeight="1">
+    <row r="271" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
     </row>
-    <row r="272" ht="11.25" customHeight="1">
+    <row r="272" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
     </row>
-    <row r="273" ht="11.25" customHeight="1">
+    <row r="273" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
     </row>
-    <row r="274" ht="11.25" customHeight="1">
+    <row r="274" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
     </row>
-    <row r="275" ht="11.25" customHeight="1">
+    <row r="275" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
     </row>
-    <row r="276" ht="11.25" customHeight="1">
+    <row r="276" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
     </row>
-    <row r="277" ht="11.25" customHeight="1">
+    <row r="277" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
     </row>
-    <row r="278" ht="11.25" customHeight="1">
+    <row r="278" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
     </row>
-    <row r="279" ht="11.25" customHeight="1">
+    <row r="279" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
     </row>
-    <row r="280" ht="11.25" customHeight="1">
+    <row r="280" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
     </row>
-    <row r="281" ht="11.25" customHeight="1">
+    <row r="281" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
     </row>
-    <row r="282" ht="11.25" customHeight="1">
+    <row r="282" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
     </row>
-    <row r="283" ht="11.25" customHeight="1">
+    <row r="283" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
     </row>
-    <row r="284" ht="11.25" customHeight="1">
+    <row r="284" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
     </row>
-    <row r="285" ht="11.25" customHeight="1">
+    <row r="285" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
     </row>
-    <row r="286" ht="11.25" customHeight="1">
+    <row r="286" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
     </row>
-    <row r="287" ht="11.25" customHeight="1">
+    <row r="287" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
     </row>
-    <row r="288" ht="11.25" customHeight="1">
+    <row r="288" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
     </row>
-    <row r="289" ht="11.25" customHeight="1">
+    <row r="289" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
     </row>
-    <row r="290" ht="11.25" customHeight="1">
+    <row r="290" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
     </row>
-    <row r="291" ht="11.25" customHeight="1">
+    <row r="291" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
     </row>
-    <row r="292" ht="11.25" customHeight="1">
+    <row r="292" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
     </row>
-    <row r="293" ht="11.25" customHeight="1">
+    <row r="293" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
     </row>
-    <row r="294" ht="11.25" customHeight="1">
+    <row r="294" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
     </row>
-    <row r="295" ht="11.25" customHeight="1">
+    <row r="295" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
     </row>
-    <row r="296" ht="11.25" customHeight="1">
+    <row r="296" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
     </row>
-    <row r="297" ht="11.25" customHeight="1">
+    <row r="297" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
     </row>
-    <row r="298" ht="11.25" customHeight="1">
+    <row r="298" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
     </row>
-    <row r="299" ht="11.25" customHeight="1">
+    <row r="299" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
     </row>
-    <row r="300" ht="11.25" customHeight="1">
+    <row r="300" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
     </row>
-    <row r="301" ht="11.25" customHeight="1">
+    <row r="301" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
     </row>
-    <row r="302" ht="11.25" customHeight="1">
+    <row r="302" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
     </row>
-    <row r="303" ht="11.25" customHeight="1">
+    <row r="303" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
     </row>
-    <row r="304" ht="11.25" customHeight="1">
+    <row r="304" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
     </row>
-    <row r="305" ht="11.25" customHeight="1">
+    <row r="305" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
     </row>
-    <row r="306" ht="11.25" customHeight="1">
+    <row r="306" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
     </row>
-    <row r="307" ht="11.25" customHeight="1">
+    <row r="307" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
     </row>
-    <row r="308" ht="11.25" customHeight="1">
+    <row r="308" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
     </row>
-    <row r="309" ht="11.25" customHeight="1">
+    <row r="309" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
     </row>
-    <row r="310" ht="11.25" customHeight="1">
+    <row r="310" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
     </row>
-    <row r="311" ht="11.25" customHeight="1">
+    <row r="311" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
     </row>
-    <row r="312" ht="11.25" customHeight="1">
+    <row r="312" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
     </row>
-    <row r="313" ht="11.25" customHeight="1">
+    <row r="313" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
     </row>
-    <row r="314" ht="11.25" customHeight="1">
+    <row r="314" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
     </row>
-    <row r="315" ht="11.25" customHeight="1">
+    <row r="315" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
     </row>
-    <row r="316" ht="11.25" customHeight="1">
+    <row r="316" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
     </row>
-    <row r="317" ht="11.25" customHeight="1">
+    <row r="317" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
     </row>
-    <row r="318" ht="11.25" customHeight="1">
+    <row r="318" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
     </row>
-    <row r="319" ht="11.25" customHeight="1">
+    <row r="319" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
     </row>
-    <row r="320" ht="11.25" customHeight="1">
+    <row r="320" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
     </row>
-    <row r="321" ht="11.25" customHeight="1">
+    <row r="321" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
     </row>
-    <row r="322" ht="11.25" customHeight="1">
+    <row r="322" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
     </row>
-    <row r="323" ht="11.25" customHeight="1">
+    <row r="323" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
     </row>
-    <row r="324" ht="11.25" customHeight="1">
+    <row r="324" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
     </row>
-    <row r="325" ht="11.25" customHeight="1">
+    <row r="325" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
     </row>
-    <row r="326" ht="11.25" customHeight="1">
+    <row r="326" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
     </row>
-    <row r="327" ht="11.25" customHeight="1">
+    <row r="327" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
     </row>
-    <row r="328" ht="11.25" customHeight="1">
+    <row r="328" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
     </row>
-    <row r="329" ht="11.25" customHeight="1">
+    <row r="329" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
     </row>
-    <row r="330" ht="11.25" customHeight="1">
+    <row r="330" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
     </row>
-    <row r="331" ht="11.25" customHeight="1">
+    <row r="331" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
     </row>
-    <row r="332" ht="11.25" customHeight="1">
+    <row r="332" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
     </row>
-    <row r="333" ht="11.25" customHeight="1">
+    <row r="333" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
     </row>
-    <row r="334" ht="11.25" customHeight="1">
+    <row r="334" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
     </row>
-    <row r="335" ht="11.25" customHeight="1">
+    <row r="335" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
     </row>
-    <row r="336" ht="11.25" customHeight="1">
+    <row r="336" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
     </row>
-    <row r="337" ht="11.25" customHeight="1">
+    <row r="337" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
     </row>
-    <row r="338" ht="11.25" customHeight="1">
+    <row r="338" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
     </row>
-    <row r="339" ht="11.25" customHeight="1">
+    <row r="339" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
     </row>
-    <row r="340" ht="11.25" customHeight="1">
+    <row r="340" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
     </row>
-    <row r="341" ht="11.25" customHeight="1">
+    <row r="341" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
     </row>
-    <row r="342" ht="11.25" customHeight="1">
+    <row r="342" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
     </row>
-    <row r="343" ht="11.25" customHeight="1">
+    <row r="343" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
     </row>
-    <row r="344" ht="11.25" customHeight="1">
+    <row r="344" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
     </row>
-    <row r="345" ht="11.25" customHeight="1">
+    <row r="345" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
     </row>
-    <row r="346" ht="11.25" customHeight="1">
+    <row r="346" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
     </row>
-    <row r="347" ht="11.25" customHeight="1">
+    <row r="347" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
     </row>
-    <row r="348" ht="11.25" customHeight="1">
+    <row r="348" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
     </row>
-    <row r="349" ht="11.25" customHeight="1">
+    <row r="349" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
     </row>
-    <row r="350" ht="11.25" customHeight="1">
+    <row r="350" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
     </row>
-    <row r="351" ht="11.25" customHeight="1">
+    <row r="351" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
     </row>
-    <row r="352" ht="11.25" customHeight="1">
+    <row r="352" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
     </row>
-    <row r="353" ht="11.25" customHeight="1">
+    <row r="353" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
     </row>
-    <row r="354" ht="11.25" customHeight="1">
+    <row r="354" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
     </row>
-    <row r="355" ht="11.25" customHeight="1">
+    <row r="355" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
     </row>
-    <row r="356" ht="11.25" customHeight="1">
+    <row r="356" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
     </row>
-    <row r="357" ht="11.25" customHeight="1">
+    <row r="357" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
     </row>
-    <row r="358" ht="11.25" customHeight="1">
+    <row r="358" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
     </row>
-    <row r="359" ht="11.25" customHeight="1">
+    <row r="359" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
     </row>
-    <row r="360" ht="11.25" customHeight="1">
+    <row r="360" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
     </row>
-    <row r="361" ht="11.25" customHeight="1">
+    <row r="361" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
     </row>
-    <row r="362" ht="11.25" customHeight="1">
+    <row r="362" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
     </row>
-    <row r="363" ht="11.25" customHeight="1">
+    <row r="363" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
     </row>
-    <row r="364" ht="11.25" customHeight="1">
+    <row r="364" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
     </row>
-    <row r="365" ht="11.25" customHeight="1">
+    <row r="365" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
     </row>
-    <row r="366" ht="11.25" customHeight="1">
+    <row r="366" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
     </row>
-    <row r="367" ht="11.25" customHeight="1">
+    <row r="367" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
     </row>
-    <row r="368" ht="11.25" customHeight="1">
+    <row r="368" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
     </row>
-    <row r="369" ht="11.25" customHeight="1">
+    <row r="369" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
     </row>
-    <row r="370" ht="11.25" customHeight="1">
+    <row r="370" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
     </row>
-    <row r="371" ht="11.25" customHeight="1">
+    <row r="371" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
     </row>
-    <row r="372" ht="11.25" customHeight="1">
+    <row r="372" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
     </row>
-    <row r="373" ht="11.25" customHeight="1">
+    <row r="373" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
     </row>
-    <row r="374" ht="11.25" customHeight="1">
+    <row r="374" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
     </row>
-    <row r="375" ht="11.25" customHeight="1">
+    <row r="375" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
     </row>
-    <row r="376" ht="11.25" customHeight="1">
+    <row r="376" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
     </row>
-    <row r="377" ht="11.25" customHeight="1">
+    <row r="377" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
     </row>
-    <row r="378" ht="11.25" customHeight="1">
+    <row r="378" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
     </row>
-    <row r="379" ht="11.25" customHeight="1">
+    <row r="379" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
     </row>
-    <row r="380" ht="11.25" customHeight="1">
+    <row r="380" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
     </row>
-    <row r="381" ht="11.25" customHeight="1">
+    <row r="381" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
     </row>
-    <row r="382" ht="11.25" customHeight="1">
+    <row r="382" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
     </row>
-    <row r="383" ht="11.25" customHeight="1">
+    <row r="383" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
     </row>
-    <row r="384" ht="11.25" customHeight="1">
+    <row r="384" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
     </row>
-    <row r="385" ht="11.25" customHeight="1">
+    <row r="385" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
     </row>
-    <row r="386" ht="11.25" customHeight="1">
+    <row r="386" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
     </row>
-    <row r="387" ht="11.25" customHeight="1">
+    <row r="387" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
     </row>
-    <row r="388" ht="11.25" customHeight="1">
+    <row r="388" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
     </row>
-    <row r="389" ht="11.25" customHeight="1">
+    <row r="389" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
     </row>
-    <row r="390" ht="11.25" customHeight="1">
+    <row r="390" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
     </row>
-    <row r="391" ht="11.25" customHeight="1">
+    <row r="391" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
     </row>
-    <row r="392" ht="11.25" customHeight="1">
+    <row r="392" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
     </row>
-    <row r="393" ht="11.25" customHeight="1">
+    <row r="393" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
     </row>
-    <row r="394" ht="11.25" customHeight="1">
+    <row r="394" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
     </row>
-    <row r="395" ht="11.25" customHeight="1">
+    <row r="395" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
     </row>
-    <row r="396" ht="11.25" customHeight="1">
+    <row r="396" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
     </row>
-    <row r="397" ht="11.25" customHeight="1">
+    <row r="397" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
     </row>
-    <row r="398" ht="11.25" customHeight="1">
+    <row r="398" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
     </row>
-    <row r="399" ht="11.25" customHeight="1">
+    <row r="399" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
     </row>
-    <row r="400" ht="11.25" customHeight="1">
+    <row r="400" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
     </row>
-    <row r="401" ht="11.25" customHeight="1">
+    <row r="401" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
     </row>
-    <row r="402" ht="11.25" customHeight="1">
+    <row r="402" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
     </row>
-    <row r="403" ht="11.25" customHeight="1">
+    <row r="403" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
     </row>
-    <row r="404" ht="11.25" customHeight="1">
+    <row r="404" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
     </row>
-    <row r="405" ht="11.25" customHeight="1">
+    <row r="405" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
     </row>
-    <row r="406" ht="11.25" customHeight="1">
+    <row r="406" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
     </row>
-    <row r="407" ht="11.25" customHeight="1">
+    <row r="407" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
     </row>
-    <row r="408" ht="11.25" customHeight="1">
+    <row r="408" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
     </row>
-    <row r="409" ht="11.25" customHeight="1">
+    <row r="409" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
     </row>
-    <row r="410" ht="11.25" customHeight="1">
+    <row r="410" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
     </row>
-    <row r="411" ht="11.25" customHeight="1">
+    <row r="411" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
     </row>
-    <row r="412" ht="11.25" customHeight="1">
+    <row r="412" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
     </row>
-    <row r="413" ht="11.25" customHeight="1">
+    <row r="413" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
     </row>
-    <row r="414" ht="11.25" customHeight="1">
+    <row r="414" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
     </row>
-    <row r="415" ht="11.25" customHeight="1">
+    <row r="415" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
     </row>
-    <row r="416" ht="11.25" customHeight="1">
+    <row r="416" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
     </row>
-    <row r="417" ht="11.25" customHeight="1">
+    <row r="417" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
     </row>
-    <row r="418" ht="11.25" customHeight="1">
+    <row r="418" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
     </row>
-    <row r="419" ht="11.25" customHeight="1">
+    <row r="419" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
     </row>
-    <row r="420" ht="11.25" customHeight="1">
+    <row r="420" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
     </row>
-    <row r="421" ht="11.25" customHeight="1">
+    <row r="421" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
     </row>
-    <row r="422" ht="11.25" customHeight="1">
+    <row r="422" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
     </row>
-    <row r="423" ht="11.25" customHeight="1">
+    <row r="423" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
     </row>
-    <row r="424" ht="11.25" customHeight="1">
+    <row r="424" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
     </row>
-    <row r="425" ht="11.25" customHeight="1">
+    <row r="425" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
     </row>
-    <row r="426" ht="11.25" customHeight="1">
+    <row r="426" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
     </row>
-    <row r="427" ht="11.25" customHeight="1">
+    <row r="427" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
     </row>
-    <row r="428" ht="11.25" customHeight="1">
+    <row r="428" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
     </row>
-    <row r="429" ht="11.25" customHeight="1">
+    <row r="429" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
     </row>
-    <row r="430" ht="11.25" customHeight="1">
+    <row r="430" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
     </row>
-    <row r="431" ht="11.25" customHeight="1">
+    <row r="431" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
     </row>
-    <row r="432" ht="11.25" customHeight="1">
+    <row r="432" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
     </row>
-    <row r="433" ht="11.25" customHeight="1">
+    <row r="433" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
     </row>
-    <row r="434" ht="11.25" customHeight="1">
+    <row r="434" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
     </row>
-    <row r="435" ht="11.25" customHeight="1">
+    <row r="435" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
     </row>
-    <row r="436" ht="11.25" customHeight="1">
+    <row r="436" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
     </row>
-    <row r="437" ht="11.25" customHeight="1">
+    <row r="437" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
     </row>
-    <row r="438" ht="11.25" customHeight="1">
+    <row r="438" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
     </row>
-    <row r="439" ht="11.25" customHeight="1">
+    <row r="439" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
     </row>
-    <row r="440" ht="11.25" customHeight="1">
+    <row r="440" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
     </row>
-    <row r="441" ht="11.25" customHeight="1">
+    <row r="441" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
     </row>
-    <row r="442" ht="11.25" customHeight="1">
+    <row r="442" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
     </row>
-    <row r="443" ht="11.25" customHeight="1">
+    <row r="443" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
     </row>
-    <row r="444" ht="11.25" customHeight="1">
+    <row r="444" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
     </row>
-    <row r="445" ht="11.25" customHeight="1">
+    <row r="445" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
     </row>
-    <row r="446" ht="11.25" customHeight="1">
+    <row r="446" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
     </row>
-    <row r="447" ht="11.25" customHeight="1">
+    <row r="447" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
     </row>
-    <row r="448" ht="11.25" customHeight="1">
+    <row r="448" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
     </row>
-    <row r="449" ht="11.25" customHeight="1">
+    <row r="449" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
     </row>
-    <row r="450" ht="11.25" customHeight="1">
+    <row r="450" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
     </row>
-    <row r="451" ht="11.25" customHeight="1">
+    <row r="451" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
     </row>
-    <row r="452" ht="11.25" customHeight="1">
+    <row r="452" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
     </row>
-    <row r="453" ht="11.25" customHeight="1">
+    <row r="453" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
     </row>
-    <row r="454" ht="11.25" customHeight="1">
+    <row r="454" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
     </row>
-    <row r="455" ht="11.25" customHeight="1">
+    <row r="455" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
     </row>
-    <row r="456" ht="11.25" customHeight="1">
+    <row r="456" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
     </row>
-    <row r="457" ht="11.25" customHeight="1">
+    <row r="457" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
     </row>
-    <row r="458" ht="11.25" customHeight="1">
+    <row r="458" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
     </row>
-    <row r="459" ht="11.25" customHeight="1">
+    <row r="459" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
     </row>
-    <row r="460" ht="11.25" customHeight="1">
+    <row r="460" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
     </row>
-    <row r="461" ht="11.25" customHeight="1">
+    <row r="461" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
     </row>
-    <row r="462" ht="11.25" customHeight="1">
+    <row r="462" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
     </row>
-    <row r="463" ht="11.25" customHeight="1">
+    <row r="463" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
     </row>
-    <row r="464" ht="11.25" customHeight="1">
+    <row r="464" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
     </row>
-    <row r="465" ht="11.25" customHeight="1">
+    <row r="465" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
     </row>
-    <row r="466" ht="11.25" customHeight="1">
+    <row r="466" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
     </row>
-    <row r="467" ht="11.25" customHeight="1">
+    <row r="467" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
     </row>
-    <row r="468" ht="11.25" customHeight="1">
+    <row r="468" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
     </row>
-    <row r="469" ht="11.25" customHeight="1">
+    <row r="469" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
     </row>
-    <row r="470" ht="11.25" customHeight="1">
+    <row r="470" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
     </row>
-    <row r="471" ht="11.25" customHeight="1">
+    <row r="471" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
     </row>
-    <row r="472" ht="11.25" customHeight="1">
+    <row r="472" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
     </row>
-    <row r="473" ht="11.25" customHeight="1">
+    <row r="473" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
     </row>
-    <row r="474" ht="11.25" customHeight="1">
+    <row r="474" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
     </row>
-    <row r="475" ht="11.25" customHeight="1">
+    <row r="475" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
     </row>
-    <row r="476" ht="11.25" customHeight="1">
+    <row r="476" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
     </row>
-    <row r="477" ht="11.25" customHeight="1">
+    <row r="477" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
     </row>
-    <row r="478" ht="11.25" customHeight="1">
+    <row r="478" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
     </row>
-    <row r="479" ht="11.25" customHeight="1">
+    <row r="479" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
     </row>
-    <row r="480" ht="11.25" customHeight="1">
+    <row r="480" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
     </row>
-    <row r="481" ht="11.25" customHeight="1">
+    <row r="481" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
     </row>
-    <row r="482" ht="11.25" customHeight="1">
+    <row r="482" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
     </row>
-    <row r="483" ht="11.25" customHeight="1">
+    <row r="483" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
     </row>
-    <row r="484" ht="11.25" customHeight="1">
+    <row r="484" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
     </row>
-    <row r="485" ht="11.25" customHeight="1">
+    <row r="485" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
     </row>
-    <row r="486" ht="11.25" customHeight="1">
+    <row r="486" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
     </row>
-    <row r="487" ht="11.25" customHeight="1">
+    <row r="487" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
     </row>
-    <row r="488" ht="11.25" customHeight="1">
+    <row r="488" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
     </row>
-    <row r="489" ht="11.25" customHeight="1">
+    <row r="489" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
     </row>
-    <row r="490" ht="11.25" customHeight="1">
+    <row r="490" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
     </row>
-    <row r="491" ht="11.25" customHeight="1">
+    <row r="491" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
     </row>
-    <row r="492" ht="11.25" customHeight="1">
+    <row r="492" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
     </row>
-    <row r="493" ht="11.25" customHeight="1">
+    <row r="493" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
     </row>
-    <row r="494" ht="11.25" customHeight="1">
+    <row r="494" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
     </row>
-    <row r="495" ht="11.25" customHeight="1">
+    <row r="495" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
     </row>
-    <row r="496" ht="11.25" customHeight="1">
+    <row r="496" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
     </row>
-    <row r="497" ht="11.25" customHeight="1">
+    <row r="497" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
     </row>
-    <row r="498" ht="11.25" customHeight="1">
+    <row r="498" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
     </row>
-    <row r="499" ht="11.25" customHeight="1">
+    <row r="499" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
     </row>
-    <row r="500" ht="11.25" customHeight="1">
+    <row r="500" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
     </row>
-    <row r="501" ht="11.25" customHeight="1">
+    <row r="501" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
     </row>
-    <row r="502" ht="11.25" customHeight="1">
+    <row r="502" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
     </row>
-    <row r="503" ht="11.25" customHeight="1">
+    <row r="503" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
     </row>
-    <row r="504" ht="11.25" customHeight="1">
+    <row r="504" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
     </row>
-    <row r="505" ht="11.25" customHeight="1">
+    <row r="505" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
     </row>
-    <row r="506" ht="11.25" customHeight="1">
+    <row r="506" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
     </row>
-    <row r="507" ht="11.25" customHeight="1">
+    <row r="507" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
     </row>
-    <row r="508" ht="11.25" customHeight="1">
+    <row r="508" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
     </row>
-    <row r="509" ht="11.25" customHeight="1">
+    <row r="509" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
     </row>
-    <row r="510" ht="11.25" customHeight="1">
+    <row r="510" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
     </row>
-    <row r="511" ht="11.25" customHeight="1">
+    <row r="511" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
     </row>
-    <row r="512" ht="11.25" customHeight="1">
+    <row r="512" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
     </row>
-    <row r="513" ht="11.25" customHeight="1">
+    <row r="513" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
     </row>
-    <row r="514" ht="11.25" customHeight="1">
+    <row r="514" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
     </row>
-    <row r="515" ht="11.25" customHeight="1">
+    <row r="515" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
     </row>
-    <row r="516" ht="11.25" customHeight="1">
+    <row r="516" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
     </row>
-    <row r="517" ht="11.25" customHeight="1">
+    <row r="517" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
     </row>
-    <row r="518" ht="11.25" customHeight="1">
+    <row r="518" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
     </row>
-    <row r="519" ht="11.25" customHeight="1">
+    <row r="519" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
     </row>
-    <row r="520" ht="11.25" customHeight="1">
+    <row r="520" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
     </row>
-    <row r="521" ht="11.25" customHeight="1">
+    <row r="521" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
     </row>
-    <row r="522" ht="11.25" customHeight="1">
+    <row r="522" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
     </row>
-    <row r="523" ht="11.25" customHeight="1">
+    <row r="523" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
     </row>
-    <row r="524" ht="11.25" customHeight="1">
+    <row r="524" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
     </row>
-    <row r="525" ht="11.25" customHeight="1">
+    <row r="525" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
     </row>
-    <row r="526" ht="11.25" customHeight="1">
+    <row r="526" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
     </row>
-    <row r="527" ht="11.25" customHeight="1">
+    <row r="527" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
     </row>
-    <row r="528" ht="11.25" customHeight="1">
+    <row r="528" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
     </row>
-    <row r="529" ht="11.25" customHeight="1">
+    <row r="529" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
     </row>
-    <row r="530" ht="11.25" customHeight="1">
+    <row r="530" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
     </row>
-    <row r="531" ht="11.25" customHeight="1">
+    <row r="531" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
     </row>
-    <row r="532" ht="11.25" customHeight="1">
+    <row r="532" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
     </row>
-    <row r="533" ht="11.25" customHeight="1">
+    <row r="533" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
     </row>
-    <row r="534" ht="11.25" customHeight="1">
+    <row r="534" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
     </row>
-    <row r="535" ht="11.25" customHeight="1">
+    <row r="535" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
     </row>
-    <row r="536" ht="11.25" customHeight="1">
+    <row r="536" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
     </row>
-    <row r="537" ht="11.25" customHeight="1">
+    <row r="537" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
     </row>
-    <row r="538" ht="11.25" customHeight="1">
+    <row r="538" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
     </row>
-    <row r="539" ht="11.25" customHeight="1">
+    <row r="539" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
     </row>
-    <row r="540" ht="11.25" customHeight="1">
+    <row r="540" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
     </row>
-    <row r="541" ht="11.25" customHeight="1">
+    <row r="541" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
     </row>
-    <row r="542" ht="11.25" customHeight="1">
+    <row r="542" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
     </row>
-    <row r="543" ht="11.25" customHeight="1">
+    <row r="543" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
     </row>
-    <row r="544" ht="11.25" customHeight="1">
+    <row r="544" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
     </row>
-    <row r="545" ht="11.25" customHeight="1">
+    <row r="545" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
     </row>
-    <row r="546" ht="11.25" customHeight="1">
+    <row r="546" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
     </row>
-    <row r="547" ht="11.25" customHeight="1">
+    <row r="547" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
     </row>
-    <row r="548" ht="11.25" customHeight="1">
+    <row r="548" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
     </row>
-    <row r="549" ht="11.25" customHeight="1">
+    <row r="549" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
     </row>
-    <row r="550" ht="11.25" customHeight="1">
+    <row r="550" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
     </row>
-    <row r="551" ht="11.25" customHeight="1">
+    <row r="551" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
     </row>
-    <row r="552" ht="11.25" customHeight="1">
+    <row r="552" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
     </row>
-    <row r="553" ht="11.25" customHeight="1">
+    <row r="553" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
     </row>
-    <row r="554" ht="11.25" customHeight="1">
+    <row r="554" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
     </row>
-    <row r="555" ht="11.25" customHeight="1">
+    <row r="555" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
     </row>
-    <row r="556" ht="11.25" customHeight="1">
+    <row r="556" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
     </row>
-    <row r="557" ht="11.25" customHeight="1">
+    <row r="557" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
     </row>
-    <row r="558" ht="11.25" customHeight="1">
+    <row r="558" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
     </row>
-    <row r="559" ht="11.25" customHeight="1">
+    <row r="559" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
     </row>
-    <row r="560" ht="11.25" customHeight="1">
+    <row r="560" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
     </row>
-    <row r="561" ht="11.25" customHeight="1">
+    <row r="561" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
     </row>
-    <row r="562" ht="11.25" customHeight="1">
+    <row r="562" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
     </row>
-    <row r="563" ht="11.25" customHeight="1">
+    <row r="563" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
     </row>
-    <row r="564" ht="11.25" customHeight="1">
+    <row r="564" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
     </row>
-    <row r="565" ht="11.25" customHeight="1">
+    <row r="565" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
     </row>
-    <row r="566" ht="11.25" customHeight="1">
+    <row r="566" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
     </row>
-    <row r="567" ht="11.25" customHeight="1">
+    <row r="567" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
     </row>
-    <row r="568" ht="11.25" customHeight="1">
+    <row r="568" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
     </row>
-    <row r="569" ht="11.25" customHeight="1">
+    <row r="569" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
     </row>
-    <row r="570" ht="11.25" customHeight="1">
+    <row r="570" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
     </row>
-    <row r="571" ht="11.25" customHeight="1">
+    <row r="571" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
     </row>
-    <row r="572" ht="11.25" customHeight="1">
+    <row r="572" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
     </row>
-    <row r="573" ht="11.25" customHeight="1">
+    <row r="573" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
     </row>
-    <row r="574" ht="11.25" customHeight="1">
+    <row r="574" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
     </row>
-    <row r="575" ht="11.25" customHeight="1">
+    <row r="575" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
     </row>
-    <row r="576" ht="11.25" customHeight="1">
+    <row r="576" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
     </row>
-    <row r="577" ht="11.25" customHeight="1">
+    <row r="577" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
     </row>
-    <row r="578" ht="11.25" customHeight="1">
+    <row r="578" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
     </row>
-    <row r="579" ht="11.25" customHeight="1">
+    <row r="579" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
     </row>
-    <row r="580" ht="11.25" customHeight="1">
+    <row r="580" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
     </row>
-    <row r="581" ht="11.25" customHeight="1">
+    <row r="581" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
     </row>
-    <row r="582" ht="11.25" customHeight="1">
+    <row r="582" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
     </row>
-    <row r="583" ht="11.25" customHeight="1">
+    <row r="583" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
     </row>
-    <row r="584" ht="11.25" customHeight="1">
+    <row r="584" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
     </row>
-    <row r="585" ht="11.25" customHeight="1">
+    <row r="585" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
     </row>
-    <row r="586" ht="11.25" customHeight="1">
+    <row r="586" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
     </row>
-    <row r="587" ht="11.25" customHeight="1">
+    <row r="587" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
     </row>
-    <row r="588" ht="11.25" customHeight="1">
+    <row r="588" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
     </row>
-    <row r="589" ht="11.25" customHeight="1">
+    <row r="589" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
     </row>
-    <row r="590" ht="11.25" customHeight="1">
+    <row r="590" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
     </row>
-    <row r="591" ht="11.25" customHeight="1">
+    <row r="591" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
     </row>
-    <row r="592" ht="11.25" customHeight="1">
+    <row r="592" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
     </row>
-    <row r="593" ht="11.25" customHeight="1">
+    <row r="593" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
     </row>
-    <row r="594" ht="11.25" customHeight="1">
+    <row r="594" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
     </row>
-    <row r="595" ht="11.25" customHeight="1">
+    <row r="595" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
     </row>
-    <row r="596" ht="11.25" customHeight="1">
+    <row r="596" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
     </row>
-    <row r="597" ht="11.25" customHeight="1">
+    <row r="597" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
     </row>
-    <row r="598" ht="11.25" customHeight="1">
+    <row r="598" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
     </row>
-    <row r="599" ht="11.25" customHeight="1">
+    <row r="599" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
     </row>
-    <row r="600" ht="11.25" customHeight="1">
+    <row r="600" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
     </row>
-    <row r="601" ht="11.25" customHeight="1">
+    <row r="601" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
     </row>
-    <row r="602" ht="11.25" customHeight="1">
+    <row r="602" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
     </row>
-    <row r="603" ht="11.25" customHeight="1">
+    <row r="603" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
     </row>
-    <row r="604" ht="11.25" customHeight="1">
+    <row r="604" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
     </row>
-    <row r="605" ht="11.25" customHeight="1">
+    <row r="605" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
     </row>
-    <row r="606" ht="11.25" customHeight="1">
+    <row r="606" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
     </row>
-    <row r="607" ht="11.25" customHeight="1">
+    <row r="607" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
     </row>
-    <row r="608" ht="11.25" customHeight="1">
+    <row r="608" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
     </row>
-    <row r="609" ht="11.25" customHeight="1">
+    <row r="609" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
     </row>
-    <row r="610" ht="11.25" customHeight="1">
+    <row r="610" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
     </row>
-    <row r="611" ht="11.25" customHeight="1">
+    <row r="611" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
     </row>
-    <row r="612" ht="11.25" customHeight="1">
+    <row r="612" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
     </row>
-    <row r="613" ht="11.25" customHeight="1">
+    <row r="613" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
     </row>
-    <row r="614" ht="11.25" customHeight="1">
+    <row r="614" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
     </row>
-    <row r="615" ht="11.25" customHeight="1">
+    <row r="615" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
     </row>
-    <row r="616" ht="11.25" customHeight="1">
+    <row r="616" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
     </row>
-    <row r="617" ht="11.25" customHeight="1">
+    <row r="617" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
     </row>
-    <row r="618" ht="11.25" customHeight="1">
+    <row r="618" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
     </row>
-    <row r="619" ht="11.25" customHeight="1">
+    <row r="619" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
     </row>
-    <row r="620" ht="11.25" customHeight="1">
+    <row r="620" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
     </row>
-    <row r="621" ht="11.25" customHeight="1">
+    <row r="621" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
     </row>
-    <row r="622" ht="11.25" customHeight="1">
+    <row r="622" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
     </row>
-    <row r="623" ht="11.25" customHeight="1">
+    <row r="623" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
     </row>
-    <row r="624" ht="11.25" customHeight="1">
+    <row r="624" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
     </row>
-    <row r="625" ht="11.25" customHeight="1">
+    <row r="625" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
     </row>
-    <row r="626" ht="11.25" customHeight="1">
+    <row r="626" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
     </row>
-    <row r="627" ht="11.25" customHeight="1">
+    <row r="627" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
     </row>
-    <row r="628" ht="11.25" customHeight="1">
+    <row r="628" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
     </row>
-    <row r="629" ht="11.25" customHeight="1">
+    <row r="629" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
     </row>
-    <row r="630" ht="11.25" customHeight="1">
+    <row r="630" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
     </row>
-    <row r="631" ht="11.25" customHeight="1">
+    <row r="631" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
     </row>
-    <row r="632" ht="11.25" customHeight="1">
+    <row r="632" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
     </row>
-    <row r="633" ht="11.25" customHeight="1">
+    <row r="633" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
     </row>
-    <row r="634" ht="11.25" customHeight="1">
+    <row r="634" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
     </row>
-    <row r="635" ht="11.25" customHeight="1">
+    <row r="635" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
     </row>
-    <row r="636" ht="11.25" customHeight="1">
+    <row r="636" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
     </row>
-    <row r="637" ht="11.25" customHeight="1">
+    <row r="637" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
     </row>
-    <row r="638" ht="11.25" customHeight="1">
+    <row r="638" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
     </row>
-    <row r="639" ht="11.25" customHeight="1">
+    <row r="639" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
     </row>
-    <row r="640" ht="11.25" customHeight="1">
+    <row r="640" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
     </row>
-    <row r="641" ht="11.25" customHeight="1">
+    <row r="641" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
     </row>
-    <row r="642" ht="11.25" customHeight="1">
+    <row r="642" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
     </row>
-    <row r="643" ht="11.25" customHeight="1">
+    <row r="643" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
     </row>
-    <row r="644" ht="11.25" customHeight="1">
+    <row r="644" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
     </row>
-    <row r="645" ht="11.25" customHeight="1">
+    <row r="645" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
     </row>
-    <row r="646" ht="11.25" customHeight="1">
+    <row r="646" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
     </row>
-    <row r="647" ht="11.25" customHeight="1">
+    <row r="647" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
     </row>
-    <row r="648" ht="11.25" customHeight="1">
+    <row r="648" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
     </row>
-    <row r="649" ht="11.25" customHeight="1">
+    <row r="649" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
     </row>
-    <row r="650" ht="11.25" customHeight="1">
+    <row r="650" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
     </row>
-    <row r="651" ht="11.25" customHeight="1">
+    <row r="651" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
     </row>
-    <row r="652" ht="11.25" customHeight="1">
+    <row r="652" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
     </row>
-    <row r="653" ht="11.25" customHeight="1">
+    <row r="653" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
     </row>
-    <row r="654" ht="11.25" customHeight="1">
+    <row r="654" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
     </row>
-    <row r="655" ht="11.25" customHeight="1">
+    <row r="655" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
     </row>
-    <row r="656" ht="11.25" customHeight="1">
+    <row r="656" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
     </row>
-    <row r="657" ht="11.25" customHeight="1">
+    <row r="657" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
     </row>
-    <row r="658" ht="11.25" customHeight="1">
+    <row r="658" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
     </row>
-    <row r="659" ht="11.25" customHeight="1">
+    <row r="659" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
     </row>
-    <row r="660" ht="11.25" customHeight="1">
+    <row r="660" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
     </row>
-    <row r="661" ht="11.25" customHeight="1">
+    <row r="661" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
     </row>
-    <row r="662" ht="11.25" customHeight="1">
+    <row r="662" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
     </row>
-    <row r="663" ht="11.25" customHeight="1">
+    <row r="663" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
     </row>
-    <row r="664" ht="11.25" customHeight="1">
+    <row r="664" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
     </row>
-    <row r="665" ht="11.25" customHeight="1">
+    <row r="665" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
     </row>
-    <row r="666" ht="11.25" customHeight="1">
+    <row r="666" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
     </row>
-    <row r="667" ht="11.25" customHeight="1">
+    <row r="667" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
     </row>
-    <row r="668" ht="11.25" customHeight="1">
+    <row r="668" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
     </row>
-    <row r="669" ht="11.25" customHeight="1">
+    <row r="669" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
     </row>
-    <row r="670" ht="11.25" customHeight="1">
+    <row r="670" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
     </row>
-    <row r="671" ht="11.25" customHeight="1">
+    <row r="671" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
     </row>
-    <row r="672" ht="11.25" customHeight="1">
+    <row r="672" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
     </row>
-    <row r="673" ht="11.25" customHeight="1">
+    <row r="673" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
     </row>
-    <row r="674" ht="11.25" customHeight="1">
+    <row r="674" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
     </row>
-    <row r="675" ht="11.25" customHeight="1">
+    <row r="675" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
     </row>
-    <row r="676" ht="11.25" customHeight="1">
+    <row r="676" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
     </row>
-    <row r="677" ht="11.25" customHeight="1">
+    <row r="677" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
     </row>
-    <row r="678" ht="11.25" customHeight="1">
+    <row r="678" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
     </row>
-    <row r="679" ht="11.25" customHeight="1">
+    <row r="679" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
     </row>
-    <row r="680" ht="11.25" customHeight="1">
+    <row r="680" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
     </row>
-    <row r="681" ht="11.25" customHeight="1">
+    <row r="681" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
     </row>
-    <row r="682" ht="11.25" customHeight="1">
+    <row r="682" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
     </row>
-    <row r="683" ht="11.25" customHeight="1">
+    <row r="683" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
     </row>
-    <row r="684" ht="11.25" customHeight="1">
+    <row r="684" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
     </row>
-    <row r="685" ht="11.25" customHeight="1">
+    <row r="685" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
     </row>
-    <row r="686" ht="11.25" customHeight="1">
+    <row r="686" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
     </row>
-    <row r="687" ht="11.25" customHeight="1">
+    <row r="687" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
     </row>
-    <row r="688" ht="11.25" customHeight="1">
+    <row r="688" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
     </row>
-    <row r="689" ht="11.25" customHeight="1">
+    <row r="689" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
     </row>
-    <row r="690" ht="11.25" customHeight="1">
+    <row r="690" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
     </row>
-    <row r="691" ht="11.25" customHeight="1">
+    <row r="691" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
     </row>
-    <row r="692" ht="11.25" customHeight="1">
+    <row r="692" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
     </row>
-    <row r="693" ht="11.25" customHeight="1">
+    <row r="693" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
     </row>
-    <row r="694" ht="11.25" customHeight="1">
+    <row r="694" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
     </row>
-    <row r="695" ht="11.25" customHeight="1">
+    <row r="695" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
     </row>
-    <row r="696" ht="11.25" customHeight="1">
+    <row r="696" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
     </row>
-    <row r="697" ht="11.25" customHeight="1">
+    <row r="697" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
     </row>
-    <row r="698" ht="11.25" customHeight="1">
+    <row r="698" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
     </row>
-    <row r="699" ht="11.25" customHeight="1">
+    <row r="699" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
     </row>
-    <row r="700" ht="11.25" customHeight="1">
+    <row r="700" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
     </row>
-    <row r="701" ht="11.25" customHeight="1">
+    <row r="701" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
     </row>
-    <row r="702" ht="11.25" customHeight="1">
+    <row r="702" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
     </row>
-    <row r="703" ht="11.25" customHeight="1">
+    <row r="703" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
     </row>
-    <row r="704" ht="11.25" customHeight="1">
+    <row r="704" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
     </row>
-    <row r="705" ht="11.25" customHeight="1">
+    <row r="705" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
     </row>
-    <row r="706" ht="11.25" customHeight="1">
+    <row r="706" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
     </row>
-    <row r="707" ht="11.25" customHeight="1">
+    <row r="707" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
     </row>
-    <row r="708" ht="11.25" customHeight="1">
+    <row r="708" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
     </row>
-    <row r="709" ht="11.25" customHeight="1">
+    <row r="709" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
     </row>
-    <row r="710" ht="11.25" customHeight="1">
+    <row r="710" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
     </row>
-    <row r="711" ht="11.25" customHeight="1">
+    <row r="711" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
     </row>
-    <row r="712" ht="11.25" customHeight="1">
+    <row r="712" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
     </row>
-    <row r="713" ht="11.25" customHeight="1">
+    <row r="713" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
     </row>
-    <row r="714" ht="11.25" customHeight="1">
+    <row r="714" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
     </row>
-    <row r="715" ht="11.25" customHeight="1">
+    <row r="715" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
     </row>
-    <row r="716" ht="11.25" customHeight="1">
+    <row r="716" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
     </row>
-    <row r="717" ht="11.25" customHeight="1">
+    <row r="717" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
     </row>
-    <row r="718" ht="11.25" customHeight="1">
+    <row r="718" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
     </row>
-    <row r="719" ht="11.25" customHeight="1">
+    <row r="719" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
     </row>
-    <row r="720" ht="11.25" customHeight="1">
+    <row r="720" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
     </row>
-    <row r="721" ht="11.25" customHeight="1">
+    <row r="721" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
     </row>
-    <row r="722" ht="11.25" customHeight="1">
+    <row r="722" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
     </row>
-    <row r="723" ht="11.25" customHeight="1">
+    <row r="723" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
     </row>
-    <row r="724" ht="11.25" customHeight="1">
+    <row r="724" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
     </row>
-    <row r="725" ht="11.25" customHeight="1">
+    <row r="725" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
     </row>
-    <row r="726" ht="11.25" customHeight="1">
+    <row r="726" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
     </row>
-    <row r="727" ht="11.25" customHeight="1">
+    <row r="727" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
     </row>
-    <row r="728" ht="11.25" customHeight="1">
+    <row r="728" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
     </row>
-    <row r="729" ht="11.25" customHeight="1">
+    <row r="729" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
     </row>
-    <row r="730" ht="11.25" customHeight="1">
+    <row r="730" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
     </row>
-    <row r="731" ht="11.25" customHeight="1">
+    <row r="731" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
     </row>
-    <row r="732" ht="11.25" customHeight="1">
+    <row r="732" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
     </row>
-    <row r="733" ht="11.25" customHeight="1">
+    <row r="733" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
     </row>
-    <row r="734" ht="11.25" customHeight="1">
+    <row r="734" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
     </row>
-    <row r="735" ht="11.25" customHeight="1">
+    <row r="735" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
     </row>
-    <row r="736" ht="11.25" customHeight="1">
+    <row r="736" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
     </row>
-    <row r="737" ht="11.25" customHeight="1">
+    <row r="737" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
     </row>
-    <row r="738" ht="11.25" customHeight="1">
+    <row r="738" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
     </row>
-    <row r="739" ht="11.25" customHeight="1">
+    <row r="739" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
     </row>
-    <row r="740" ht="11.25" customHeight="1">
+    <row r="740" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
     </row>
-    <row r="741" ht="11.25" customHeight="1">
+    <row r="741" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
     </row>
-    <row r="742" ht="11.25" customHeight="1">
+    <row r="742" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
     </row>
-    <row r="743" ht="11.25" customHeight="1">
+    <row r="743" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
     </row>
-    <row r="744" ht="11.25" customHeight="1">
+    <row r="744" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
     </row>
-    <row r="745" ht="11.25" customHeight="1">
+    <row r="745" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
     </row>
-    <row r="746" ht="11.25" customHeight="1">
+    <row r="746" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
     </row>
-    <row r="747" ht="11.25" customHeight="1">
+    <row r="747" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
     </row>
-    <row r="748" ht="11.25" customHeight="1">
+    <row r="748" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
     </row>
-    <row r="749" ht="11.25" customHeight="1">
+    <row r="749" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
     </row>
-    <row r="750" ht="11.25" customHeight="1">
+    <row r="750" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
     </row>
-    <row r="751" ht="11.25" customHeight="1">
+    <row r="751" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
     </row>
-    <row r="752" ht="11.25" customHeight="1">
+    <row r="752" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
     </row>
-    <row r="753" ht="11.25" customHeight="1">
+    <row r="753" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
     </row>
-    <row r="754" ht="11.25" customHeight="1">
+    <row r="754" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
     </row>
-    <row r="755" ht="11.25" customHeight="1">
+    <row r="755" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
     </row>
-    <row r="756" ht="11.25" customHeight="1">
+    <row r="756" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
     </row>
-    <row r="757" ht="11.25" customHeight="1">
+    <row r="757" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
     </row>
-    <row r="758" ht="11.25" customHeight="1">
+    <row r="758" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
     </row>
-    <row r="759" ht="11.25" customHeight="1">
+    <row r="759" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
     </row>
-    <row r="760" ht="11.25" customHeight="1">
+    <row r="760" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
     </row>
-    <row r="761" ht="11.25" customHeight="1">
+    <row r="761" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
     </row>
-    <row r="762" ht="11.25" customHeight="1">
+    <row r="762" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
     </row>
-    <row r="763" ht="11.25" customHeight="1">
+    <row r="763" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
     </row>
-    <row r="764" ht="11.25" customHeight="1">
+    <row r="764" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
     </row>
-    <row r="765" ht="11.25" customHeight="1">
+    <row r="765" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
     </row>
-    <row r="766" ht="11.25" customHeight="1">
+    <row r="766" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
     </row>
-    <row r="767" ht="11.25" customHeight="1">
+    <row r="767" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
     </row>
-    <row r="768" ht="11.25" customHeight="1">
+    <row r="768" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
     </row>
-    <row r="769" ht="11.25" customHeight="1">
+    <row r="769" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
     </row>
-    <row r="770" ht="11.25" customHeight="1">
+    <row r="770" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
     </row>
-    <row r="771" ht="11.25" customHeight="1">
+    <row r="771" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
     </row>
-    <row r="772" ht="11.25" customHeight="1">
+    <row r="772" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
     </row>
-    <row r="773" ht="11.25" customHeight="1">
+    <row r="773" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
     </row>
-    <row r="774" ht="11.25" customHeight="1">
+    <row r="774" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
     </row>
-    <row r="775" ht="11.25" customHeight="1">
+    <row r="775" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
     </row>
-    <row r="776" ht="11.25" customHeight="1">
+    <row r="776" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
     </row>
-    <row r="777" ht="11.25" customHeight="1">
+    <row r="777" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
     </row>
-    <row r="778" ht="11.25" customHeight="1">
+    <row r="778" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
     </row>
-    <row r="779" ht="11.25" customHeight="1">
+    <row r="779" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
     </row>
-    <row r="780" ht="11.25" customHeight="1">
+    <row r="780" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
     </row>
-    <row r="781" ht="11.25" customHeight="1">
+    <row r="781" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
     </row>
-    <row r="782" ht="11.25" customHeight="1">
+    <row r="782" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
     </row>
-    <row r="783" ht="11.25" customHeight="1">
+    <row r="783" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
     </row>
-    <row r="784" ht="11.25" customHeight="1">
+    <row r="784" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
     </row>
-    <row r="785" ht="11.25" customHeight="1">
+    <row r="785" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
     </row>
-    <row r="786" ht="11.25" customHeight="1">
+    <row r="786" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
     </row>
-    <row r="787" ht="11.25" customHeight="1">
+    <row r="787" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
     </row>
-    <row r="788" ht="11.25" customHeight="1">
+    <row r="788" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
     </row>
-    <row r="789" ht="11.25" customHeight="1">
+    <row r="789" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
     </row>
-    <row r="790" ht="11.25" customHeight="1">
+    <row r="790" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
     </row>
-    <row r="791" ht="11.25" customHeight="1">
+    <row r="791" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
     </row>
-    <row r="792" ht="11.25" customHeight="1">
+    <row r="792" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
     </row>
-    <row r="793" ht="11.25" customHeight="1">
+    <row r="793" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
     </row>
-    <row r="794" ht="11.25" customHeight="1">
+    <row r="794" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
     </row>
-    <row r="795" ht="11.25" customHeight="1">
+    <row r="795" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
     </row>
-    <row r="796" ht="11.25" customHeight="1">
+    <row r="796" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
     </row>
-    <row r="797" ht="11.25" customHeight="1">
+    <row r="797" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
     </row>
-    <row r="798" ht="11.25" customHeight="1">
+    <row r="798" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
     </row>
-    <row r="799" ht="11.25" customHeight="1">
+    <row r="799" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
     </row>
-    <row r="800" ht="11.25" customHeight="1">
+    <row r="800" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
     </row>
-    <row r="801" ht="11.25" customHeight="1">
+    <row r="801" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
     </row>
-    <row r="802" ht="11.25" customHeight="1">
+    <row r="802" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
     </row>
-    <row r="803" ht="11.25" customHeight="1">
+    <row r="803" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
     </row>
-    <row r="804" ht="11.25" customHeight="1">
+    <row r="804" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
     </row>
-    <row r="805" ht="11.25" customHeight="1">
+    <row r="805" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
     </row>
-    <row r="806" ht="11.25" customHeight="1">
+    <row r="806" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
     </row>
-    <row r="807" ht="11.25" customHeight="1">
+    <row r="807" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
     </row>
-    <row r="808" ht="11.25" customHeight="1">
+    <row r="808" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
     </row>
-    <row r="809" ht="11.25" customHeight="1">
+    <row r="809" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
     </row>
-    <row r="810" ht="11.25" customHeight="1">
+    <row r="810" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
     </row>
-    <row r="811" ht="11.25" customHeight="1">
+    <row r="811" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
     </row>
-    <row r="812" ht="11.25" customHeight="1">
+    <row r="812" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
     </row>
-    <row r="813" ht="11.25" customHeight="1">
+    <row r="813" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
     </row>
-    <row r="814" ht="11.25" customHeight="1">
+    <row r="814" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
     </row>
-    <row r="815" ht="11.25" customHeight="1">
+    <row r="815" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
     </row>
-    <row r="816" ht="11.25" customHeight="1">
+    <row r="816" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
     </row>
-    <row r="817" ht="11.25" customHeight="1">
+    <row r="817" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
     </row>
-    <row r="818" ht="11.25" customHeight="1">
+    <row r="818" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
     </row>
-    <row r="819" ht="11.25" customHeight="1">
+    <row r="819" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
     </row>
-    <row r="820" ht="11.25" customHeight="1">
+    <row r="820" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
     </row>
-    <row r="821" ht="11.25" customHeight="1">
+    <row r="821" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
     </row>
-    <row r="822" ht="11.25" customHeight="1">
+    <row r="822" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
     </row>
-    <row r="823" ht="11.25" customHeight="1">
+    <row r="823" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
     </row>
-    <row r="824" ht="11.25" customHeight="1">
+    <row r="824" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
     </row>
-    <row r="825" ht="11.25" customHeight="1">
+    <row r="825" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
     </row>
-    <row r="826" ht="11.25" customHeight="1">
+    <row r="826" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
     </row>
-    <row r="827" ht="11.25" customHeight="1">
+    <row r="827" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
     </row>
-    <row r="828" ht="11.25" customHeight="1">
+    <row r="828" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
     </row>
-    <row r="829" ht="11.25" customHeight="1">
+    <row r="829" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
     </row>
-    <row r="830" ht="11.25" customHeight="1">
+    <row r="830" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
     </row>
-    <row r="831" ht="11.25" customHeight="1">
+    <row r="831" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
     </row>
-    <row r="832" ht="11.25" customHeight="1">
+    <row r="832" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
     </row>
-    <row r="833" ht="11.25" customHeight="1">
+    <row r="833" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
     </row>
-    <row r="834" ht="11.25" customHeight="1">
+    <row r="834" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
     </row>
-    <row r="835" ht="11.25" customHeight="1">
+    <row r="835" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
     </row>
-    <row r="836" ht="11.25" customHeight="1">
+    <row r="836" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
     </row>
-    <row r="837" ht="11.25" customHeight="1">
+    <row r="837" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
     </row>
-    <row r="838" ht="11.25" customHeight="1">
+    <row r="838" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
     </row>
-    <row r="839" ht="11.25" customHeight="1">
+    <row r="839" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
     </row>
-    <row r="840" ht="11.25" customHeight="1">
+    <row r="840" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
     </row>
-    <row r="841" ht="11.25" customHeight="1">
+    <row r="841" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
     </row>
-    <row r="842" ht="11.25" customHeight="1">
+    <row r="842" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
     </row>
-    <row r="843" ht="11.25" customHeight="1">
+    <row r="843" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
     </row>
-    <row r="844" ht="11.25" customHeight="1">
+    <row r="844" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
     </row>
-    <row r="845" ht="11.25" customHeight="1">
+    <row r="845" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
     </row>
-    <row r="846" ht="11.25" customHeight="1">
+    <row r="846" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
     </row>
-    <row r="847" ht="11.25" customHeight="1">
+    <row r="847" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
     </row>
-    <row r="848" ht="11.25" customHeight="1">
+    <row r="848" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
     </row>
-    <row r="849" ht="11.25" customHeight="1">
+    <row r="849" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
     </row>
-    <row r="850" ht="11.25" customHeight="1">
+    <row r="850" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
     </row>
-    <row r="851" ht="11.25" customHeight="1">
+    <row r="851" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
     </row>
-    <row r="852" ht="11.25" customHeight="1">
+    <row r="852" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
     </row>
-    <row r="853" ht="11.25" customHeight="1">
+    <row r="853" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
     </row>
-    <row r="854" ht="11.25" customHeight="1">
+    <row r="854" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
     </row>
-    <row r="855" ht="11.25" customHeight="1">
+    <row r="855" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
     </row>
-    <row r="856" ht="11.25" customHeight="1">
+    <row r="856" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
     </row>
-    <row r="857" ht="11.25" customHeight="1">
+    <row r="857" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
     </row>
-    <row r="858" ht="11.25" customHeight="1">
+    <row r="858" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
     </row>
-    <row r="859" ht="11.25" customHeight="1">
+    <row r="859" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
     </row>
-    <row r="860" ht="11.25" customHeight="1">
+    <row r="860" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
     </row>
-    <row r="861" ht="11.25" customHeight="1">
+    <row r="861" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
     </row>
-    <row r="862" ht="11.25" customHeight="1">
+    <row r="862" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
     </row>
-    <row r="863" ht="11.25" customHeight="1">
+    <row r="863" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
     </row>
-    <row r="864" ht="11.25" customHeight="1">
+    <row r="864" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
     </row>
-    <row r="865" ht="11.25" customHeight="1">
+    <row r="865" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
     </row>
-    <row r="866" ht="11.25" customHeight="1">
+    <row r="866" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
     </row>
-    <row r="867" ht="11.25" customHeight="1">
+    <row r="867" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
     </row>
-    <row r="868" ht="11.25" customHeight="1">
+    <row r="868" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
     </row>
-    <row r="869" ht="11.25" customHeight="1">
+    <row r="869" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
     </row>
-    <row r="870" ht="11.25" customHeight="1">
+    <row r="870" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
     </row>
-    <row r="871" ht="11.25" customHeight="1">
+    <row r="871" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
     </row>
-    <row r="872" ht="11.25" customHeight="1">
+    <row r="872" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
     </row>
-    <row r="873" ht="11.25" customHeight="1">
+    <row r="873" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
     </row>
-    <row r="874" ht="11.25" customHeight="1">
+    <row r="874" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
     </row>
-    <row r="875" ht="11.25" customHeight="1">
+    <row r="875" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
     </row>
-    <row r="876" ht="11.25" customHeight="1">
+    <row r="876" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
     </row>
-    <row r="877" ht="11.25" customHeight="1">
+    <row r="877" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
     </row>
-    <row r="878" ht="11.25" customHeight="1">
+    <row r="878" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
     </row>
-    <row r="879" ht="11.25" customHeight="1">
+    <row r="879" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
     </row>
-    <row r="880" ht="11.25" customHeight="1">
+    <row r="880" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
     </row>
-    <row r="881" ht="11.25" customHeight="1">
+    <row r="881" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
     </row>
-    <row r="882" ht="11.25" customHeight="1">
+    <row r="882" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
     </row>
-    <row r="883" ht="11.25" customHeight="1">
+    <row r="883" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
     </row>
-    <row r="884" ht="11.25" customHeight="1">
+    <row r="884" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
     </row>
-    <row r="885" ht="11.25" customHeight="1">
+    <row r="885" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
     </row>
-    <row r="886" ht="11.25" customHeight="1">
+    <row r="886" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
     </row>
-    <row r="887" ht="11.25" customHeight="1">
+    <row r="887" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
     </row>
-    <row r="888" ht="11.25" customHeight="1">
+    <row r="888" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
     </row>
-    <row r="889" ht="11.25" customHeight="1">
+    <row r="889" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
     </row>
-    <row r="890" ht="11.25" customHeight="1">
+    <row r="890" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
     </row>
-    <row r="891" ht="11.25" customHeight="1">
+    <row r="891" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
     </row>
-    <row r="892" ht="11.25" customHeight="1">
+    <row r="892" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
     </row>
-    <row r="893" ht="11.25" customHeight="1">
+    <row r="893" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
     </row>
-    <row r="894" ht="11.25" customHeight="1">
+    <row r="894" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
     </row>
-    <row r="895" ht="11.25" customHeight="1">
+    <row r="895" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
     </row>
-    <row r="896" ht="11.25" customHeight="1">
+    <row r="896" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
     </row>
-    <row r="897" ht="11.25" customHeight="1">
+    <row r="897" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
     </row>
-    <row r="898" ht="11.25" customHeight="1">
+    <row r="898" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
     </row>
-    <row r="899" ht="11.25" customHeight="1">
+    <row r="899" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
     </row>
-    <row r="900" ht="11.25" customHeight="1">
+    <row r="900" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
     </row>
-    <row r="901" ht="11.25" customHeight="1">
+    <row r="901" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
     </row>
-    <row r="902" ht="11.25" customHeight="1">
+    <row r="902" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
     </row>
-    <row r="903" ht="11.25" customHeight="1">
+    <row r="903" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
     </row>
-    <row r="904" ht="11.25" customHeight="1">
+    <row r="904" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
     </row>
-    <row r="905" ht="11.25" customHeight="1">
+    <row r="905" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
     </row>
-    <row r="906" ht="11.25" customHeight="1">
+    <row r="906" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
     </row>
-    <row r="907" ht="11.25" customHeight="1">
+    <row r="907" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
     </row>
-    <row r="908" ht="11.25" customHeight="1">
+    <row r="908" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
     </row>
-    <row r="909" ht="11.25" customHeight="1">
+    <row r="909" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
     </row>
-    <row r="910" ht="11.25" customHeight="1">
+    <row r="910" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
     </row>
-    <row r="911" ht="11.25" customHeight="1">
+    <row r="911" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
     </row>
-    <row r="912" ht="11.25" customHeight="1">
+    <row r="912" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
     </row>
-    <row r="913" ht="11.25" customHeight="1">
+    <row r="913" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
     </row>
-    <row r="914" ht="11.25" customHeight="1">
+    <row r="914" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
     </row>
-    <row r="915" ht="11.25" customHeight="1">
+    <row r="915" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
     </row>
-    <row r="916" ht="11.25" customHeight="1">
+    <row r="916" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
     </row>
-    <row r="917" ht="11.25" customHeight="1">
+    <row r="917" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
     </row>
-    <row r="918" ht="11.25" customHeight="1">
+    <row r="918" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
     </row>
-    <row r="919" ht="11.25" customHeight="1">
+    <row r="919" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
     </row>
-    <row r="920" ht="11.25" customHeight="1">
+    <row r="920" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
     </row>
-    <row r="921" ht="11.25" customHeight="1">
+    <row r="921" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
     </row>
-    <row r="922" ht="11.25" customHeight="1">
+    <row r="922" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
     </row>
-    <row r="923" ht="11.25" customHeight="1">
+    <row r="923" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
     </row>
-    <row r="924" ht="11.25" customHeight="1">
+    <row r="924" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
     </row>
-    <row r="925" ht="11.25" customHeight="1">
+    <row r="925" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
     </row>
-    <row r="926" ht="11.25" customHeight="1">
+    <row r="926" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
     </row>
-    <row r="927" ht="11.25" customHeight="1">
+    <row r="927" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
     </row>
-    <row r="928" ht="11.25" customHeight="1">
+    <row r="928" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
     </row>
-    <row r="929" ht="11.25" customHeight="1">
+    <row r="929" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
     </row>
-    <row r="930" ht="11.25" customHeight="1">
+    <row r="930" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
     </row>
-    <row r="931" ht="11.25" customHeight="1">
+    <row r="931" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
     </row>
-    <row r="932" ht="11.25" customHeight="1">
+    <row r="932" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
     </row>
-    <row r="933" ht="11.25" customHeight="1">
+    <row r="933" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
     </row>
-    <row r="934" ht="11.25" customHeight="1">
+    <row r="934" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
     </row>
-    <row r="935" ht="11.25" customHeight="1">
+    <row r="935" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
     </row>
-    <row r="936" ht="11.25" customHeight="1">
+    <row r="936" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
     </row>
-    <row r="937" ht="11.25" customHeight="1">
+    <row r="937" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
     </row>
-    <row r="938" ht="11.25" customHeight="1">
+    <row r="938" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
     </row>
-    <row r="939" ht="11.25" customHeight="1">
+    <row r="939" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
     </row>
-    <row r="940" ht="11.25" customHeight="1">
+    <row r="940" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
     </row>
-    <row r="941" ht="11.25" customHeight="1">
+    <row r="941" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
     </row>
-    <row r="942" ht="11.25" customHeight="1">
+    <row r="942" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
     </row>
-    <row r="943" ht="11.25" customHeight="1">
+    <row r="943" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
     </row>
-    <row r="944" ht="11.25" customHeight="1">
+    <row r="944" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
     </row>
-    <row r="945" ht="11.25" customHeight="1">
+    <row r="945" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
     </row>
-    <row r="946" ht="11.25" customHeight="1">
+    <row r="946" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
     </row>
-    <row r="947" ht="11.25" customHeight="1">
+    <row r="947" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
     </row>
-    <row r="948" ht="11.25" customHeight="1">
+    <row r="948" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
     </row>
-    <row r="949" ht="11.25" customHeight="1">
+    <row r="949" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
     </row>
-    <row r="950" ht="11.25" customHeight="1">
+    <row r="950" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
     </row>
-    <row r="951" ht="11.25" customHeight="1">
+    <row r="951" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
     </row>
-    <row r="952" ht="11.25" customHeight="1">
+    <row r="952" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
     </row>
-    <row r="953" ht="11.25" customHeight="1">
+    <row r="953" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
     </row>
-    <row r="954" ht="11.25" customHeight="1">
+    <row r="954" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
     </row>
-    <row r="955" ht="11.25" customHeight="1">
+    <row r="955" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
     </row>
-    <row r="956" ht="11.25" customHeight="1">
+    <row r="956" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
     </row>
-    <row r="957" ht="11.25" customHeight="1">
+    <row r="957" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
     </row>
-    <row r="958" ht="11.25" customHeight="1">
+    <row r="958" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
     </row>
-    <row r="959" ht="11.25" customHeight="1">
+    <row r="959" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
     </row>
-    <row r="960" ht="11.25" customHeight="1">
+    <row r="960" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
     </row>
-    <row r="961" ht="11.25" customHeight="1">
+    <row r="961" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
     </row>
-    <row r="962" ht="11.25" customHeight="1">
+    <row r="962" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
     </row>
-    <row r="963" ht="11.25" customHeight="1">
+    <row r="963" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
     </row>
-    <row r="964" ht="11.25" customHeight="1">
+    <row r="964" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
     </row>
-    <row r="965" ht="11.25" customHeight="1">
+    <row r="965" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
     </row>
-    <row r="966" ht="11.25" customHeight="1">
+    <row r="966" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
     </row>
-    <row r="967" ht="11.25" customHeight="1">
+    <row r="967" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
     </row>
-    <row r="968" ht="11.25" customHeight="1">
+    <row r="968" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
     </row>
-    <row r="969" ht="11.25" customHeight="1">
+    <row r="969" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
     </row>
-    <row r="970" ht="11.25" customHeight="1">
+    <row r="970" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
     </row>
-    <row r="971" ht="11.25" customHeight="1">
+    <row r="971" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
     </row>
-    <row r="972" ht="11.25" customHeight="1">
+    <row r="972" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
     </row>
-    <row r="973" ht="11.25" customHeight="1">
+    <row r="973" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
     </row>
-    <row r="974" ht="11.25" customHeight="1">
+    <row r="974" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
     </row>
-    <row r="975" ht="11.25" customHeight="1">
+    <row r="975" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
     </row>
-    <row r="976" ht="11.25" customHeight="1">
+    <row r="976" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
     </row>
-    <row r="977" ht="11.25" customHeight="1">
+    <row r="977" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
     </row>
-    <row r="978" ht="11.25" customHeight="1">
+    <row r="978" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
     </row>
-    <row r="979" ht="11.25" customHeight="1">
+    <row r="979" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
     </row>
-    <row r="980" ht="11.25" customHeight="1">
+    <row r="980" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
     </row>
-    <row r="981" ht="11.25" customHeight="1">
+    <row r="981" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
     </row>
-    <row r="982" ht="11.25" customHeight="1">
+    <row r="982" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
     </row>
-    <row r="983" ht="11.25" customHeight="1">
+    <row r="983" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
     </row>
-    <row r="984" ht="11.25" customHeight="1">
+    <row r="984" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
     </row>
-    <row r="985" ht="11.25" customHeight="1">
+    <row r="985" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
     </row>
-    <row r="986" ht="11.25" customHeight="1">
+    <row r="986" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
     </row>
-    <row r="987" ht="11.25" customHeight="1">
+    <row r="987" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
     </row>
-    <row r="988" ht="11.25" customHeight="1">
+    <row r="988" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
     </row>
-    <row r="989" ht="11.25" customHeight="1">
+    <row r="989" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
     </row>
-    <row r="990" ht="11.25" customHeight="1">
+    <row r="990" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
     </row>
-    <row r="991" ht="11.25" customHeight="1">
+    <row r="991" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
     </row>
-    <row r="992" ht="11.25" customHeight="1">
+    <row r="992" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
     </row>
-    <row r="993" ht="11.25" customHeight="1">
+    <row r="993" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
     </row>
-    <row r="994" ht="11.25" customHeight="1">
+    <row r="994" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
     </row>
-    <row r="995" ht="11.25" customHeight="1">
+    <row r="995" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
     </row>
-    <row r="996" ht="11.25" customHeight="1">
+    <row r="996" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
     </row>
-    <row r="997" ht="11.25" customHeight="1">
+    <row r="997" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
     </row>
-    <row r="998" ht="11.25" customHeight="1">
+    <row r="998" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
     </row>
-    <row r="999" ht="11.25" customHeight="1">
+    <row r="999" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
     </row>
-    <row r="1000" ht="11.25" customHeight="1">
+    <row r="1000" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
     </row>
-    <row r="1001" ht="11.25" customHeight="1">
+    <row r="1001" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="2"/>
       <c r="B1001" s="2"/>
     </row>
-    <row r="1002" ht="11.25" customHeight="1">
+    <row r="1002" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="2"/>
       <c r="B1002" s="2"/>
     </row>
-    <row r="1003" ht="11.25" customHeight="1">
+    <row r="1003" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="2"/>
       <c r="B1003" s="2"/>
     </row>
-    <row r="1004" ht="11.25" customHeight="1">
+    <row r="1004" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="2"/>
       <c r="B1004" s="2"/>
     </row>
-    <row r="1005" ht="11.25" customHeight="1">
+    <row r="1005" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="2"/>
       <c r="B1005" s="2"/>
     </row>
-    <row r="1006" ht="11.25" customHeight="1">
+    <row r="1006" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="2"/>
       <c r="B1006" s="2"/>
     </row>
-    <row r="1007" ht="11.25" customHeight="1">
+    <row r="1007" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="2"/>
       <c r="B1007" s="2"/>
     </row>
-    <row r="1008" ht="11.25" customHeight="1">
+    <row r="1008" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="2"/>
       <c r="B1008" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
     <mergeCell ref="A172:B172"/>
     <mergeCell ref="A173:B173"/>
     <mergeCell ref="A175:B175"/>
@@ -8312,59 +8418,8 @@
     <mergeCell ref="A160:B160"/>
     <mergeCell ref="A164:B164"/>
     <mergeCell ref="A169:B169"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A102:B102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A105:B105"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A111:B111"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="A135:B135"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="A140:B140"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.25" right="0.25" top="0.75"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>